--- a/Financial Analysis/LRN.xlsx
+++ b/Financial Analysis/LRN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1FAD95E-F57E-4961-BA00-3B83644B0C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F32ACD-6643-4950-9DDE-1E8A3A0480A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7397855C-6173-4C21-9C59-A8371E1F4110}"/>
   </bookViews>
@@ -777,14 +777,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>144.5</v>
+        <v>140.65</v>
       </c>
       <c r="E3" s="3">
-        <v>45923</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45923</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="3">
         <v>45967</v>
@@ -808,7 +808,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>6242.4000000000005</v>
+        <v>6076.0800000000008</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -849,7 +849,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>5673.4000000000005</v>
+        <v>5507.0800000000008</v>
       </c>
     </row>
   </sheetData>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="AQ25" s="4">
         <f>Main!D3</f>
-        <v>144.5</v>
+        <v>140.65</v>
       </c>
     </row>
     <row r="26" spans="2:43" x14ac:dyDescent="0.3">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AQ26" s="12">
         <f>AQ24/AQ25-1</f>
-        <v>0.40036474043573977</v>
+        <v>0.43869680051876569</v>
       </c>
     </row>
     <row r="27" spans="2:43" x14ac:dyDescent="0.3">

--- a/Financial Analysis/LRN.xlsx
+++ b/Financial Analysis/LRN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F32ACD-6643-4950-9DDE-1E8A3A0480A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAA247C-B5F5-491E-A042-253906D3A93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7397855C-6173-4C21-9C59-A8371E1F4110}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>Price</t>
   </si>
@@ -236,10 +236,7 @@
     <t>Q426</t>
   </si>
   <si>
-    <t>Q425 8K</t>
-  </si>
-  <si>
-    <t>Undervalued</t>
+    <t>Heavily undervalued</t>
   </si>
 </sst>
 </file>
@@ -354,13 +351,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -378,7 +375,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13251180" y="7620"/>
+          <a:off x="13975080" y="7620"/>
           <a:ext cx="0" cy="6316980"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -777,17 +774,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>140.65</v>
+        <v>70.83</v>
       </c>
       <c r="E3" s="3">
-        <v>45937</v>
+        <v>45960</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45961</v>
       </c>
       <c r="G3" s="3">
-        <v>45967</v>
+        <v>46049</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -795,11 +792,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="5">
-        <f>43.2</f>
-        <v>43.2</v>
+        <f>43.4</f>
+        <v>43.4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -808,7 +805,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>6076.0800000000008</v>
+        <v>3074.0219999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -816,11 +813,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="5">
-        <f>782.5+202.8</f>
-        <v>985.3</v>
+        <f>518.4+196.7</f>
+        <v>715.09999999999991</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -828,10 +825,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="5">
-        <v>416.3</v>
+        <f>416.8</f>
+        <v>416.8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -840,7 +838,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>569</v>
+        <v>298.2999999999999</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -849,7 +847,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>5507.0800000000008</v>
+        <v>2775.7220000000002</v>
       </c>
     </row>
   </sheetData>
@@ -859,18 +857,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B736A5B-3953-46B2-B63C-0DC83568B8DF}">
-  <dimension ref="B1:ER27"/>
+  <dimension ref="B1:ES27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="18" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="19" max="22" width="10.5546875" customWidth="1"/>
     <col min="24" max="40" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="17.5546875" customWidth="1"/>
+    <col min="41" max="41" width="10.5546875" customWidth="1"/>
+    <col min="43" max="43" width="12" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:149" x14ac:dyDescent="0.3">
       <c r="C1" s="9">
         <v>44469</v>
       </c>
@@ -982,8 +981,11 @@
       <c r="AN1" s="9">
         <v>49490</v>
       </c>
+      <c r="AO1" s="9">
+        <v>49490</v>
+      </c>
     </row>
-    <row r="2" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:149" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>24</v>
       </c>
@@ -1095,8 +1097,11 @@
       <c r="AN2">
         <v>2035</v>
       </c>
+      <c r="AO2">
+        <v>2035</v>
+      </c>
     </row>
-    <row r="3" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1152,20 +1157,18 @@
         <v>653.6</v>
       </c>
       <c r="S3" s="8">
-        <f>O3*1.22</f>
-        <v>672.34199999999998</v>
+        <v>620.9</v>
       </c>
       <c r="T3" s="8">
-        <f>P3*1.2</f>
-        <v>704.64</v>
+        <v>630</v>
       </c>
       <c r="U3" s="8">
-        <f>Q3*1.18</f>
-        <v>723.8119999999999</v>
+        <f>Q3*1.03</f>
+        <v>631.80200000000002</v>
       </c>
       <c r="V3" s="8">
-        <f>R3*1.15</f>
-        <v>751.64</v>
+        <f>R3*1</f>
+        <v>653.6</v>
       </c>
       <c r="X3" s="8">
         <v>1015.8</v>
@@ -1191,46 +1194,50 @@
       </c>
       <c r="AE3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>2852.4339999999997</v>
+        <v>2536.3020000000001</v>
       </c>
       <c r="AF3" s="8">
-        <f>AE3*1.13</f>
-        <v>3223.2504199999994</v>
+        <f>AE3*1.04</f>
+        <v>2637.7540800000002</v>
       </c>
       <c r="AG3" s="8">
-        <f>AF3*1.08</f>
-        <v>3481.1104535999998</v>
+        <f>AF3*1.03</f>
+        <v>2716.8867024000001</v>
       </c>
       <c r="AH3" s="8">
-        <f>AG3*1.05</f>
-        <v>3655.16597628</v>
+        <f>AG3*1.02</f>
+        <v>2771.2244364480002</v>
       </c>
       <c r="AI3" s="8">
-        <f>AH3*1.04</f>
-        <v>3801.3726153312</v>
+        <f>AH3*1.02</f>
+        <v>2826.6489251769603</v>
       </c>
       <c r="AJ3" s="8">
-        <f>AI3*1.03</f>
-        <v>3915.413793791136</v>
+        <f>AI3*1.02</f>
+        <v>2883.1819036804995</v>
       </c>
       <c r="AK3" s="8">
-        <f t="shared" ref="AK3:AN3" si="0">AJ3*1.02</f>
-        <v>3993.7220696669588</v>
+        <f t="shared" ref="AK3:AO3" si="0">AJ3*1.02</f>
+        <v>2940.8455417541095</v>
       </c>
       <c r="AL3" s="8">
         <f t="shared" si="0"/>
-        <v>4073.5965110602979</v>
+        <v>2999.6624525891916</v>
       </c>
       <c r="AM3" s="8">
         <f t="shared" si="0"/>
-        <v>4155.0684412815035</v>
+        <v>3059.6557016409756</v>
       </c>
       <c r="AN3" s="8">
         <f t="shared" si="0"/>
-        <v>4238.1698101071333</v>
+        <v>3120.8488156737953</v>
+      </c>
+      <c r="AO3" s="8">
+        <f t="shared" si="0"/>
+        <v>3183.2657919872713</v>
       </c>
     </row>
-    <row r="4" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>13</v>
       </c>
@@ -1286,20 +1293,19 @@
         <v>414.7</v>
       </c>
       <c r="S4" s="5">
-        <f>S3-S5</f>
-        <v>403.40519999999998</v>
+        <v>378.8</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" ref="T4:V4" si="1">T3-T5</f>
-        <v>422.78399999999999</v>
+        <v>378</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="1"/>
-        <v>434.28719999999993</v>
+        <v>379.08119999999997</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" si="1"/>
-        <v>450.98399999999998</v>
+        <v>392.16</v>
       </c>
       <c r="X4" s="5">
         <v>663.4</v>
@@ -1325,199 +1331,207 @@
       </c>
       <c r="AE4" s="5">
         <f>SUM(S4:V4)</f>
-        <v>1711.4603999999999</v>
+        <v>1528.0411999999999</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" ref="AF4:AN4" si="2">AF3-AF5</f>
-        <v>1901.7177477999996</v>
+        <v>1556.2749072000001</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="2"/>
-        <v>2053.8551676239999</v>
+        <v>1602.9631544160002</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="2"/>
-        <v>2156.5479260051998</v>
+        <v>1635.0224175043202</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="2"/>
-        <v>2242.8098430454083</v>
+        <v>1667.7228658544066</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="2"/>
-        <v>2310.0941383367704</v>
+        <v>1701.0773231714948</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="2"/>
-        <v>2356.2960211035061</v>
+        <v>1735.0988696349248</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="2"/>
-        <v>2403.4219415255757</v>
+        <v>1769.8008470276231</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="2"/>
-        <v>2451.4903803560874</v>
+        <v>1805.1968639681756</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" si="2"/>
-        <v>2500.5201879632086</v>
+        <v>1841.3008012475393</v>
+      </c>
+      <c r="AO4" s="5">
+        <f t="shared" ref="AO4" si="3">AO3-AO5</f>
+        <v>1878.1268172724901</v>
       </c>
     </row>
-    <row r="5" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:R5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:S5" si="4">C3-C4</f>
         <v>126.39999999999998</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>147.5</v>
       </c>
       <c r="E5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>154.80000000000001</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>167.79999999999995</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>129.69999999999999</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>170.09999999999997</v>
       </c>
       <c r="I5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>175.3</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>172.00000000000017</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>172.89999999999998</v>
       </c>
       <c r="L5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>201.2</v>
       </c>
       <c r="M5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>201.29999999999995</v>
       </c>
       <c r="N5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>188.2000000000001</v>
       </c>
       <c r="O5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>215.90000000000003</v>
       </c>
       <c r="P5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>239.80000000000007</v>
       </c>
       <c r="Q5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>249.29999999999995</v>
       </c>
       <c r="R5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>238.90000000000003</v>
       </c>
       <c r="S5" s="8">
-        <f>S3*0.4</f>
-        <v>268.93680000000001</v>
+        <f t="shared" si="4"/>
+        <v>242.09999999999997</v>
       </c>
       <c r="T5" s="8">
-        <f t="shared" ref="T5:V5" si="4">T3*0.4</f>
-        <v>281.85599999999999</v>
+        <f t="shared" ref="T5:V5" si="5">T3*0.4</f>
+        <v>252</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" si="4"/>
-        <v>289.52479999999997</v>
+        <f t="shared" si="5"/>
+        <v>252.72080000000003</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" si="4"/>
-        <v>300.65600000000001</v>
+        <f t="shared" si="5"/>
+        <v>261.44</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" ref="X5:AE5" si="5">X3-X4</f>
+        <f t="shared" ref="X5:AE5" si="6">X3-X4</f>
         <v>352.4</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>347.59999999999991</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>534.9</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>596.5</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>647.10000000000014</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>763.59999999999991</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>943.90000000000032</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" si="5"/>
-        <v>1140.9735999999998</v>
+        <f t="shared" si="6"/>
+        <v>1008.2608000000002</v>
       </c>
       <c r="AF5" s="8">
         <f>AF3*0.41</f>
-        <v>1321.5326721999998</v>
+        <v>1081.4791728</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" ref="AG5:AN5" si="6">AG3*0.41</f>
-        <v>1427.2552859759999</v>
+        <f t="shared" ref="AG5:AN5" si="7">AG3*0.41</f>
+        <v>1113.9235479839999</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" si="6"/>
-        <v>1498.6180502748</v>
+        <f t="shared" si="7"/>
+        <v>1136.2020189436801</v>
       </c>
       <c r="AI5" s="8">
-        <f t="shared" si="6"/>
-        <v>1558.5627722857919</v>
+        <f t="shared" si="7"/>
+        <v>1158.9260593225538</v>
       </c>
       <c r="AJ5" s="8">
-        <f t="shared" si="6"/>
-        <v>1605.3196554543656</v>
+        <f t="shared" si="7"/>
+        <v>1182.1045805090048</v>
       </c>
       <c r="AK5" s="8">
-        <f t="shared" si="6"/>
-        <v>1637.4260485634529</v>
+        <f t="shared" si="7"/>
+        <v>1205.7466721191847</v>
       </c>
       <c r="AL5" s="8">
-        <f t="shared" si="6"/>
-        <v>1670.174569534722</v>
+        <f t="shared" si="7"/>
+        <v>1229.8616055615685</v>
       </c>
       <c r="AM5" s="8">
-        <f t="shared" si="6"/>
-        <v>1703.5780609254164</v>
+        <f t="shared" si="7"/>
+        <v>1254.4588376728</v>
       </c>
       <c r="AN5" s="8">
-        <f t="shared" si="6"/>
-        <v>1737.6496221439245</v>
+        <f t="shared" si="7"/>
+        <v>1279.548014426256</v>
+      </c>
+      <c r="AO5" s="8">
+        <f t="shared" ref="AO5" si="8">AO3*0.41</f>
+        <v>1305.1389747147812</v>
       </c>
     </row>
-    <row r="6" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>15</v>
       </c>
@@ -1573,8 +1587,7 @@
         <v>122.6</v>
       </c>
       <c r="S6" s="5">
-        <f>O6*1.05</f>
-        <v>176.92500000000001</v>
+        <v>173.1</v>
       </c>
       <c r="T6" s="5">
         <f>P6*1.03</f>
@@ -1612,46 +1625,50 @@
       </c>
       <c r="AE6" s="5">
         <f>SUM(S6:V6)</f>
-        <v>541.09100000000001</v>
+        <v>537.26599999999996</v>
       </c>
       <c r="AF6" s="5">
         <f>AE6*1.02</f>
-        <v>551.91282000000001</v>
+        <v>548.01131999999996</v>
       </c>
       <c r="AG6" s="5">
         <f>AF6*1.01</f>
-        <v>557.43194819999997</v>
+        <v>553.49143319999996</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" ref="AH6:AN6" si="7">AG6*1.01</f>
-        <v>563.00626768199993</v>
+        <f t="shared" ref="AH6:AO6" si="9">AG6*1.01</f>
+        <v>559.02634753199993</v>
       </c>
       <c r="AI6" s="5">
-        <f t="shared" si="7"/>
-        <v>568.63633035881992</v>
+        <f t="shared" si="9"/>
+        <v>564.61661100731999</v>
       </c>
       <c r="AJ6" s="5">
-        <f t="shared" si="7"/>
-        <v>574.32269366240814</v>
+        <f t="shared" si="9"/>
+        <v>570.26277711739317</v>
       </c>
       <c r="AK6" s="5">
-        <f t="shared" si="7"/>
-        <v>580.06592059903221</v>
+        <f t="shared" si="9"/>
+        <v>575.96540488856715</v>
       </c>
       <c r="AL6" s="5">
-        <f t="shared" si="7"/>
-        <v>585.86657980502252</v>
+        <f t="shared" si="9"/>
+        <v>581.72505893745279</v>
       </c>
       <c r="AM6" s="5">
-        <f t="shared" si="7"/>
-        <v>591.72524560307272</v>
+        <f t="shared" si="9"/>
+        <v>587.54230952682735</v>
       </c>
       <c r="AN6" s="5">
-        <f t="shared" si="7"/>
-        <v>597.64249805910345</v>
+        <f t="shared" si="9"/>
+        <v>593.41773262209563</v>
+      </c>
+      <c r="AO6" s="5">
+        <f t="shared" si="9"/>
+        <v>599.35190994831657</v>
       </c>
     </row>
-    <row r="7" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>53</v>
       </c>
@@ -1697,69 +1714,70 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
+      <c r="AO7" s="5"/>
     </row>
-    <row r="8" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="8">
-        <f t="shared" ref="C8:Q8" si="8">C5-C6</f>
+        <f t="shared" ref="C8:Q8" si="10">C5-C6</f>
         <v>-7.0000000000000284</v>
       </c>
       <c r="D8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>56.900000000000006</v>
       </c>
       <c r="E8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>60.600000000000009</v>
       </c>
       <c r="F8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>46.199999999999932</v>
       </c>
       <c r="G8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-28.700000000000017</v>
       </c>
       <c r="H8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>68.099999999999966</v>
       </c>
       <c r="I8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>126.10000000000016</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3.2999999999999829</v>
       </c>
       <c r="L8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>84.299999999999983</v>
       </c>
       <c r="M8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>88.299999999999955</v>
       </c>
       <c r="N8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>73.700000000000074</v>
       </c>
       <c r="O8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>47.400000000000034</v>
       </c>
       <c r="P8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>125.00000000000007</v>
       </c>
       <c r="Q8" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>130.79999999999995</v>
       </c>
       <c r="R8" s="8">
@@ -1767,43 +1785,43 @@
         <v>56.80000000000004</v>
       </c>
       <c r="S8" s="8">
-        <f t="shared" ref="S8:V8" si="9">S5-S6-S7</f>
-        <v>92.011799999999994</v>
+        <f t="shared" ref="S8:V8" si="11">S5-S6-S7</f>
+        <v>68.999999999999972</v>
       </c>
       <c r="T8" s="8">
-        <f t="shared" si="9"/>
-        <v>163.61199999999999</v>
+        <f t="shared" si="11"/>
+        <v>133.756</v>
       </c>
       <c r="U8" s="8">
-        <f t="shared" si="9"/>
-        <v>168.65479999999997</v>
+        <f t="shared" si="11"/>
+        <v>131.85080000000002</v>
       </c>
       <c r="V8" s="8">
-        <f t="shared" si="9"/>
-        <v>175.60400000000001</v>
+        <f t="shared" si="11"/>
+        <v>136.38800000000001</v>
       </c>
       <c r="X8" s="8">
-        <f t="shared" ref="X8:AC8" si="10">X5-X6</f>
+        <f t="shared" ref="X8:AC8" si="12">X5-X6</f>
         <v>45.599999999999966</v>
       </c>
       <c r="Y8" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>32.499999999999886</v>
       </c>
       <c r="Z8" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>110.5</v>
       </c>
       <c r="AA8" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>156.69999999999999</v>
       </c>
       <c r="AB8" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>165.50000000000011</v>
       </c>
       <c r="AC8" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>249.59999999999991</v>
       </c>
       <c r="AD8" s="8">
@@ -1811,47 +1829,51 @@
         <v>360.00000000000034</v>
       </c>
       <c r="AE8" s="8">
-        <f t="shared" ref="AE8:AN8" si="11">AE5-AE6</f>
-        <v>599.8825999999998</v>
+        <f t="shared" ref="AE8:AN8" si="13">AE5-AE6</f>
+        <v>470.99480000000028</v>
       </c>
       <c r="AF8" s="8">
-        <f t="shared" si="11"/>
-        <v>769.61985219999974</v>
+        <f t="shared" si="13"/>
+        <v>533.46785280000006</v>
       </c>
       <c r="AG8" s="8">
-        <f t="shared" si="11"/>
-        <v>869.8233377759999</v>
+        <f t="shared" si="13"/>
+        <v>560.43211478399996</v>
       </c>
       <c r="AH8" s="8">
-        <f t="shared" si="11"/>
-        <v>935.61178259280007</v>
+        <f t="shared" si="13"/>
+        <v>577.17567141168013</v>
       </c>
       <c r="AI8" s="8">
-        <f t="shared" si="11"/>
-        <v>989.92644192697196</v>
+        <f t="shared" si="13"/>
+        <v>594.30944831523379</v>
       </c>
       <c r="AJ8" s="8">
-        <f t="shared" si="11"/>
-        <v>1030.9969617919573</v>
+        <f t="shared" si="13"/>
+        <v>611.84180339161162</v>
       </c>
       <c r="AK8" s="8">
-        <f t="shared" si="11"/>
-        <v>1057.3601279644208</v>
+        <f t="shared" si="13"/>
+        <v>629.78126723061757</v>
       </c>
       <c r="AL8" s="8">
-        <f t="shared" si="11"/>
-        <v>1084.3079897296993</v>
+        <f t="shared" si="13"/>
+        <v>648.13654662411568</v>
       </c>
       <c r="AM8" s="8">
-        <f t="shared" si="11"/>
-        <v>1111.8528153223438</v>
+        <f t="shared" si="13"/>
+        <v>666.91652814597262</v>
       </c>
       <c r="AN8" s="8">
-        <f t="shared" si="11"/>
-        <v>1140.007124084821</v>
+        <f t="shared" si="13"/>
+        <v>686.1302818041604</v>
+      </c>
+      <c r="AO8" s="8">
+        <f t="shared" ref="AO8" si="14">AO5-AO6</f>
+        <v>705.7870647664646</v>
       </c>
     </row>
-    <row r="9" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -1865,7 +1887,7 @@
         <v>2.4</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" ref="F9:F10" si="12">AA9-E9-D9-C9</f>
+        <f t="shared" ref="F9:F10" si="15">AA9-E9-D9-C9</f>
         <v>-3</v>
       </c>
       <c r="G9" s="5">
@@ -1878,7 +1900,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J10" si="13">AB9-I9-H9-G9</f>
+        <f t="shared" ref="J9:J10" si="16">AB9-I9-H9-G9</f>
         <v>2.0999999999999996</v>
       </c>
       <c r="K9" s="5">
@@ -1907,7 +1929,7 @@
         <v>2.7</v>
       </c>
       <c r="S9" s="5">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T9" s="5">
         <v>3</v>
@@ -1941,47 +1963,51 @@
         <v>10.6</v>
       </c>
       <c r="AE9" s="5">
-        <f t="shared" ref="AE9:AE10" si="14">SUM(S9:V9)</f>
-        <v>12</v>
+        <f t="shared" ref="AE9:AE10" si="17">SUM(S9:V9)</f>
+        <v>12.1</v>
       </c>
       <c r="AF9" s="5">
-        <f t="shared" ref="AF9:AN9" si="15">AE9*1.03</f>
-        <v>12.36</v>
+        <f t="shared" ref="AF9:AO9" si="18">AE9*1.03</f>
+        <v>12.462999999999999</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" si="15"/>
-        <v>12.7308</v>
+        <f t="shared" si="18"/>
+        <v>12.83689</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" si="15"/>
-        <v>13.112724</v>
+        <f t="shared" si="18"/>
+        <v>13.2219967</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" si="15"/>
-        <v>13.506105720000001</v>
+        <f t="shared" si="18"/>
+        <v>13.618656601</v>
       </c>
       <c r="AJ9" s="5">
-        <f t="shared" si="15"/>
-        <v>13.911288891600002</v>
+        <f t="shared" si="18"/>
+        <v>14.02721629903</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" si="15"/>
-        <v>14.328627558348002</v>
+        <f t="shared" si="18"/>
+        <v>14.4480327880009</v>
       </c>
       <c r="AL9" s="5">
-        <f t="shared" si="15"/>
-        <v>14.758486385098442</v>
+        <f t="shared" si="18"/>
+        <v>14.881473771640927</v>
       </c>
       <c r="AM9" s="5">
-        <f t="shared" si="15"/>
-        <v>15.201240976651395</v>
+        <f t="shared" si="18"/>
+        <v>15.327917984790155</v>
       </c>
       <c r="AN9" s="5">
-        <f t="shared" si="15"/>
-        <v>15.657278205950936</v>
+        <f t="shared" si="18"/>
+        <v>15.787755524333859</v>
+      </c>
+      <c r="AO9" s="5">
+        <f t="shared" si="18"/>
+        <v>16.261388190063876</v>
       </c>
     </row>
-    <row r="10" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -1995,7 +2021,7 @@
         <v>-0.5</v>
       </c>
       <c r="F10" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>3.7</v>
       </c>
       <c r="G10" s="5">
@@ -2008,7 +2034,7 @@
         <v>-4.5999999999999996</v>
       </c>
       <c r="J10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-5.9</v>
       </c>
       <c r="K10" s="5">
@@ -2037,7 +2063,7 @@
         <v>-10.199999999999999</v>
       </c>
       <c r="S10" s="5">
-        <v>-10</v>
+        <v>-16.899999999999999</v>
       </c>
       <c r="T10" s="5">
         <v>-10</v>
@@ -2071,200 +2097,208 @@
         <v>-33.700000000000003</v>
       </c>
       <c r="AE10" s="5">
-        <f t="shared" si="14"/>
-        <v>-40</v>
+        <f t="shared" si="17"/>
+        <v>-46.9</v>
       </c>
       <c r="AF10" s="5">
-        <f t="shared" ref="AF10:AN10" si="16">AE10*1.03</f>
-        <v>-41.2</v>
+        <f t="shared" ref="AF10:AO10" si="19">AE10*1.03</f>
+        <v>-48.307000000000002</v>
       </c>
       <c r="AG10" s="5">
-        <f t="shared" si="16"/>
-        <v>-42.436000000000007</v>
+        <f t="shared" si="19"/>
+        <v>-49.756210000000003</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="16"/>
-        <v>-43.709080000000007</v>
+        <f t="shared" si="19"/>
+        <v>-51.248896300000006</v>
       </c>
       <c r="AI10" s="5">
-        <f t="shared" si="16"/>
-        <v>-45.020352400000007</v>
+        <f t="shared" si="19"/>
+        <v>-52.786363189000006</v>
       </c>
       <c r="AJ10" s="5">
-        <f t="shared" si="16"/>
-        <v>-46.370962972000008</v>
+        <f t="shared" si="19"/>
+        <v>-54.369954084670006</v>
       </c>
       <c r="AK10" s="5">
-        <f t="shared" si="16"/>
-        <v>-47.762091861160009</v>
+        <f t="shared" si="19"/>
+        <v>-56.001052707210107</v>
       </c>
       <c r="AL10" s="5">
-        <f t="shared" si="16"/>
-        <v>-49.194954616994814</v>
+        <f t="shared" si="19"/>
+        <v>-57.681084288426412</v>
       </c>
       <c r="AM10" s="5">
-        <f t="shared" si="16"/>
-        <v>-50.670803255504659</v>
+        <f t="shared" si="19"/>
+        <v>-59.411516817079203</v>
       </c>
       <c r="AN10" s="5">
-        <f t="shared" si="16"/>
-        <v>-52.190927353169798</v>
+        <f t="shared" si="19"/>
+        <v>-61.193862321591581</v>
+      </c>
+      <c r="AO10" s="5">
+        <f t="shared" si="19"/>
+        <v>-63.029678191239327</v>
       </c>
     </row>
-    <row r="11" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="8">
-        <f t="shared" ref="C11:R11" si="17">C8-C9-C10</f>
+        <f t="shared" ref="C11:R11" si="20">C8-C9-C10</f>
         <v>-16.000000000000028</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>58.900000000000006</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>58.70000000000001</v>
       </c>
       <c r="F11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>45.499999999999929</v>
       </c>
       <c r="G11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>-29.700000000000017</v>
       </c>
       <c r="H11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>69.999999999999972</v>
       </c>
       <c r="I11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>2.3999999999999995</v>
       </c>
       <c r="J11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>129.90000000000018</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>6.3999999999999826</v>
       </c>
       <c r="L11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>88.799999999999983</v>
       </c>
       <c r="M11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>93.599999999999952</v>
       </c>
       <c r="N11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>78.900000000000077</v>
       </c>
       <c r="O11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>53.80000000000004</v>
       </c>
       <c r="P11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>129.60000000000008</v>
       </c>
       <c r="Q11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>135.39999999999995</v>
       </c>
       <c r="R11" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>64.30000000000004</v>
       </c>
       <c r="S11" s="8">
-        <f t="shared" ref="S11" si="18">S8-S9-S10</f>
-        <v>99.011799999999994</v>
+        <f t="shared" ref="S11" si="21">S8-S9-S10</f>
+        <v>82.799999999999983</v>
       </c>
       <c r="T11" s="8">
-        <f t="shared" ref="T11" si="19">T8-T9-T10</f>
-        <v>170.61199999999999</v>
+        <f t="shared" ref="T11" si="22">T8-T9-T10</f>
+        <v>140.756</v>
       </c>
       <c r="U11" s="8">
-        <f t="shared" ref="U11" si="20">U8-U9-U10</f>
-        <v>175.65479999999997</v>
+        <f t="shared" ref="U11" si="23">U8-U9-U10</f>
+        <v>138.85080000000002</v>
       </c>
       <c r="V11" s="8">
-        <f t="shared" ref="V11" si="21">V8-V9-V10</f>
-        <v>182.60400000000001</v>
+        <f t="shared" ref="V11" si="24">V8-V9-V10</f>
+        <v>143.38800000000001</v>
       </c>
       <c r="X11" s="8">
-        <f t="shared" ref="X11:AE11" si="22">X8-X9-X10</f>
+        <f t="shared" ref="X11:AE11" si="25">X8-X9-X10</f>
         <v>48.499999999999964</v>
       </c>
       <c r="Y11" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>33.499999999999886</v>
       </c>
       <c r="Z11" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>95.3</v>
       </c>
       <c r="AA11" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>147.09999999999997</v>
       </c>
       <c r="AB11" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>172.60000000000011</v>
       </c>
       <c r="AC11" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>267.69999999999987</v>
       </c>
       <c r="AD11" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>383.10000000000031</v>
       </c>
       <c r="AE11" s="8">
-        <f t="shared" si="22"/>
-        <v>627.8825999999998</v>
+        <f t="shared" si="25"/>
+        <v>505.79480000000024</v>
       </c>
       <c r="AF11" s="8">
-        <f t="shared" ref="AF11:AN11" si="23">AF8-AF9-AF10</f>
-        <v>798.45985219999977</v>
+        <f t="shared" ref="AF11:AN11" si="26">AF8-AF9-AF10</f>
+        <v>569.31185280000011</v>
       </c>
       <c r="AG11" s="8">
-        <f t="shared" si="23"/>
-        <v>899.52853777599989</v>
+        <f t="shared" si="26"/>
+        <v>597.35143478399993</v>
       </c>
       <c r="AH11" s="8">
-        <f t="shared" si="23"/>
-        <v>966.20813859280008</v>
+        <f t="shared" si="26"/>
+        <v>615.20257101168011</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" si="23"/>
-        <v>1021.4406886069719</v>
+        <f t="shared" si="26"/>
+        <v>633.47715490323378</v>
       </c>
       <c r="AJ11" s="8">
-        <f t="shared" si="23"/>
-        <v>1063.4566358723573</v>
+        <f t="shared" si="26"/>
+        <v>652.18454117725162</v>
       </c>
       <c r="AK11" s="8">
-        <f t="shared" si="23"/>
-        <v>1090.793592267233</v>
+        <f t="shared" si="26"/>
+        <v>671.33428714982676</v>
       </c>
       <c r="AL11" s="8">
-        <f t="shared" si="23"/>
-        <v>1118.7444579615958</v>
+        <f t="shared" si="26"/>
+        <v>690.93615714090117</v>
       </c>
       <c r="AM11" s="8">
-        <f t="shared" si="23"/>
-        <v>1147.3223776011969</v>
+        <f t="shared" si="26"/>
+        <v>711.00012697826173</v>
       </c>
       <c r="AN11" s="8">
-        <f t="shared" si="23"/>
-        <v>1176.54077323204</v>
+        <f t="shared" si="26"/>
+        <v>731.53638860141814</v>
+      </c>
+      <c r="AO11" s="8">
+        <f t="shared" ref="AO11" si="27">AO8-AO9-AO10</f>
+        <v>752.5553547676401</v>
       </c>
     </row>
-    <row r="12" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>20</v>
       </c>
@@ -2278,7 +2312,7 @@
         <v>16.7</v>
       </c>
       <c r="F12" s="5">
-        <f t="shared" ref="F12:F13" si="24">AA12-E12-D12-C12</f>
+        <f t="shared" ref="F12:F13" si="28">AA12-E12-D12-C12</f>
         <v>10.400000000000002</v>
       </c>
       <c r="G12" s="5">
@@ -2291,7 +2325,7 @@
         <v>19.5</v>
       </c>
       <c r="J12" s="5">
-        <f t="shared" ref="J12:J13" si="25">AB12-I12-H12-G12</f>
+        <f t="shared" ref="J12:J13" si="29">AB12-I12-H12-G12</f>
         <v>14.399999999999999</v>
       </c>
       <c r="K12" s="5">
@@ -2320,20 +2354,19 @@
         <v>12.9</v>
       </c>
       <c r="S12" s="5">
-        <f>S11*0.24</f>
-        <v>23.762831999999996</v>
+        <v>14.4</v>
       </c>
       <c r="T12" s="5">
-        <f t="shared" ref="T12:V12" si="26">T11*0.24</f>
-        <v>40.94688</v>
+        <f t="shared" ref="T12:V12" si="30">T11*0.24</f>
+        <v>33.781439999999996</v>
       </c>
       <c r="U12" s="5">
-        <f t="shared" si="26"/>
-        <v>42.157151999999989</v>
+        <f t="shared" si="30"/>
+        <v>33.324192000000004</v>
       </c>
       <c r="V12" s="5">
-        <f t="shared" si="26"/>
-        <v>43.824960000000004</v>
+        <f t="shared" si="30"/>
+        <v>34.413119999999999</v>
       </c>
       <c r="X12" s="5">
         <v>10.5</v>
@@ -2358,47 +2391,51 @@
         <v>93.100000000000009</v>
       </c>
       <c r="AE12" s="5">
-        <f t="shared" ref="AE12:AE13" si="27">SUM(S12:V12)</f>
-        <v>150.691824</v>
+        <f t="shared" ref="AE12:AE13" si="31">SUM(S12:V12)</f>
+        <v>115.91875199999998</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" ref="AF12:AN12" si="28">AF11*0.25</f>
-        <v>199.61496304999994</v>
+        <f t="shared" ref="AF12:AN12" si="32">AF11*0.25</f>
+        <v>142.32796320000003</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="28"/>
-        <v>224.88213444399997</v>
+        <f t="shared" si="32"/>
+        <v>149.33785869599998</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="28"/>
-        <v>241.55203464820002</v>
+        <f t="shared" si="32"/>
+        <v>153.80064275292003</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="28"/>
-        <v>255.36017215174297</v>
+        <f t="shared" si="32"/>
+        <v>158.36928872580845</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="28"/>
-        <v>265.86415896808933</v>
+        <f t="shared" si="32"/>
+        <v>163.0461352943129</v>
       </c>
       <c r="AK12" s="5">
-        <f t="shared" si="28"/>
-        <v>272.69839806680824</v>
+        <f t="shared" si="32"/>
+        <v>167.83357178745669</v>
       </c>
       <c r="AL12" s="5">
-        <f t="shared" si="28"/>
-        <v>279.68611449039895</v>
+        <f t="shared" si="32"/>
+        <v>172.73403928522529</v>
       </c>
       <c r="AM12" s="5">
-        <f t="shared" si="28"/>
-        <v>286.83059440029922</v>
+        <f t="shared" si="32"/>
+        <v>177.75003174456543</v>
       </c>
       <c r="AN12" s="5">
-        <f t="shared" si="28"/>
-        <v>294.13519330801</v>
+        <f t="shared" si="32"/>
+        <v>182.88409715035453</v>
+      </c>
+      <c r="AO12" s="5">
+        <f t="shared" ref="AO12" si="33">AO11*0.25</f>
+        <v>188.13883869191002</v>
       </c>
     </row>
-    <row r="13" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>21</v>
       </c>
@@ -2412,7 +2449,7 @@
         <v>-0.9</v>
       </c>
       <c r="F13" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.10000000000000003</v>
       </c>
       <c r="G13" s="5">
@@ -2425,7 +2462,7 @@
         <v>-0.4</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>-0.20000000000000007</v>
       </c>
       <c r="K13" s="5">
@@ -2454,7 +2491,7 @@
         <v>0.1</v>
       </c>
       <c r="S13" s="5">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="T13" s="5">
         <v>0</v>
@@ -2488,632 +2525,640 @@
         <v>2.3000000000000003</v>
       </c>
       <c r="AE13" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>-0.4</v>
       </c>
       <c r="AF13" s="5">
-        <f t="shared" ref="AF13:AN13" si="29">AF11*0.01</f>
-        <v>7.984598521999998</v>
+        <f t="shared" ref="AF13:AN13" si="34">AF11*0.01</f>
+        <v>5.6931185280000012</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" si="29"/>
-        <v>8.9952853777599984</v>
+        <f t="shared" si="34"/>
+        <v>5.9735143478399992</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="29"/>
-        <v>9.6620813859280013</v>
+        <f t="shared" si="34"/>
+        <v>6.152025710116801</v>
       </c>
       <c r="AI13" s="5">
-        <f t="shared" si="29"/>
-        <v>10.214406886069719</v>
+        <f t="shared" si="34"/>
+        <v>6.3347715490323377</v>
       </c>
       <c r="AJ13" s="5">
-        <f t="shared" si="29"/>
-        <v>10.634566358723573</v>
+        <f t="shared" si="34"/>
+        <v>6.5218454117725164</v>
       </c>
       <c r="AK13" s="5">
-        <f t="shared" si="29"/>
-        <v>10.90793592267233</v>
+        <f t="shared" si="34"/>
+        <v>6.7133428714982681</v>
       </c>
       <c r="AL13" s="5">
-        <f t="shared" si="29"/>
-        <v>11.187444579615958</v>
+        <f t="shared" si="34"/>
+        <v>6.9093615714090122</v>
       </c>
       <c r="AM13" s="5">
-        <f t="shared" si="29"/>
-        <v>11.473223776011968</v>
+        <f t="shared" si="34"/>
+        <v>7.1100012697826172</v>
       </c>
       <c r="AN13" s="5">
-        <f t="shared" si="29"/>
-        <v>11.7654077323204</v>
+        <f t="shared" si="34"/>
+        <v>7.3153638860141816</v>
+      </c>
+      <c r="AO13" s="5">
+        <f t="shared" ref="AO13" si="35">AO11*0.01</f>
+        <v>7.5255535476764015</v>
       </c>
     </row>
-    <row r="14" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="8">
-        <f t="shared" ref="C14:S14" si="30">C11-C12-C13</f>
+        <f t="shared" ref="C14:S14" si="36">C11-C12-C13</f>
         <v>-12.800000000000027</v>
       </c>
       <c r="D14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>42.000000000000007</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>42.900000000000013</v>
       </c>
       <c r="F14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>34.999999999999922</v>
       </c>
       <c r="G14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>-22.700000000000017</v>
       </c>
       <c r="H14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>50.699999999999974</v>
       </c>
       <c r="I14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>-16.700000000000003</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>115.70000000000017</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>4.8999999999999826</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>66.799999999999983</v>
       </c>
       <c r="M14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>69.699999999999946</v>
       </c>
       <c r="N14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>62.800000000000082</v>
       </c>
       <c r="O14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>40.900000000000041</v>
       </c>
       <c r="P14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>96.200000000000074</v>
       </c>
       <c r="Q14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>99.299999999999955</v>
       </c>
       <c r="R14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>51.30000000000004</v>
       </c>
       <c r="S14" s="8">
-        <f t="shared" si="30"/>
-        <v>75.248967999999991</v>
+        <f t="shared" si="36"/>
+        <v>68.799999999999983</v>
       </c>
       <c r="T14" s="8">
-        <f t="shared" ref="T14" si="31">T11-T12-T13</f>
-        <v>129.66512</v>
+        <f t="shared" ref="T14" si="37">T11-T12-T13</f>
+        <v>106.97456</v>
       </c>
       <c r="U14" s="8">
-        <f t="shared" ref="U14" si="32">U11-U12-U13</f>
-        <v>133.49764799999997</v>
+        <f t="shared" ref="U14" si="38">U11-U12-U13</f>
+        <v>105.52660800000001</v>
       </c>
       <c r="V14" s="8">
-        <f t="shared" ref="V14" si="33">V11-V12-V13</f>
-        <v>138.77904000000001</v>
+        <f t="shared" ref="V14" si="39">V11-V12-V13</f>
+        <v>108.97488000000001</v>
       </c>
       <c r="X14" s="8">
-        <f t="shared" ref="X14:AE14" si="34">X11-X12-X13</f>
+        <f t="shared" ref="X14:AE14" si="40">X11-X12-X13</f>
         <v>37.399999999999963</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>24.599999999999888</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>71.5</v>
       </c>
       <c r="AA14" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>107.09999999999997</v>
       </c>
       <c r="AB14" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>127.00000000000011</v>
       </c>
       <c r="AC14" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>204.19999999999987</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>287.70000000000027</v>
       </c>
       <c r="AE14" s="8">
-        <f t="shared" si="34"/>
-        <v>477.1907759999998</v>
+        <f t="shared" si="40"/>
+        <v>390.27604800000023</v>
       </c>
       <c r="AF14" s="8">
-        <f t="shared" ref="AF14:AN14" si="35">AF11-AF12-AF13</f>
-        <v>590.86029062799992</v>
+        <f t="shared" ref="AF14:AN14" si="41">AF11-AF12-AF13</f>
+        <v>421.2907710720001</v>
       </c>
       <c r="AG14" s="8">
-        <f t="shared" si="35"/>
-        <v>665.65111795423991</v>
+        <f t="shared" si="41"/>
+        <v>442.0400617401599</v>
       </c>
       <c r="AH14" s="8">
-        <f t="shared" si="35"/>
-        <v>714.9940225586721</v>
+        <f t="shared" si="41"/>
+        <v>455.24990254864332</v>
       </c>
       <c r="AI14" s="8">
-        <f t="shared" si="35"/>
-        <v>755.86610956915922</v>
+        <f t="shared" si="41"/>
+        <v>468.77309462839298</v>
       </c>
       <c r="AJ14" s="8">
-        <f t="shared" si="35"/>
-        <v>786.95791054554445</v>
+        <f t="shared" si="41"/>
+        <v>482.61656047116622</v>
       </c>
       <c r="AK14" s="8">
-        <f t="shared" si="35"/>
-        <v>807.18725827775233</v>
+        <f t="shared" si="41"/>
+        <v>496.78737249087186</v>
       </c>
       <c r="AL14" s="8">
-        <f t="shared" si="35"/>
-        <v>827.87089889158085</v>
+        <f t="shared" si="41"/>
+        <v>511.29275628426683</v>
       </c>
       <c r="AM14" s="8">
-        <f t="shared" si="35"/>
-        <v>849.01855942488567</v>
+        <f t="shared" si="41"/>
+        <v>526.14009396391373</v>
       </c>
       <c r="AN14" s="8">
-        <f t="shared" si="35"/>
-        <v>870.64017219170955</v>
-      </c>
-      <c r="AO14" s="1">
-        <f>AN14*(1+$AQ$19)</f>
-        <v>861.93377046979242</v>
+        <f t="shared" si="41"/>
+        <v>541.33692756504934</v>
+      </c>
+      <c r="AO14" s="8">
+        <f t="shared" ref="AO14" si="42">AO11-AO12-AO13</f>
+        <v>556.89096252805371</v>
       </c>
       <c r="AP14" s="1">
-        <f t="shared" ref="AP14:DA14" si="36">AO14*(1+$AQ$19)</f>
-        <v>853.31443276509447</v>
+        <f>AO14*(1+$AR$19)</f>
+        <v>551.32205290277318</v>
       </c>
       <c r="AQ14" s="1">
-        <f t="shared" si="36"/>
-        <v>844.78128843744355</v>
+        <f t="shared" ref="AQ14:DB14" si="43">AP14*(1+$AR$19)</f>
+        <v>545.80883237374542</v>
       </c>
       <c r="AR14" s="1">
-        <f t="shared" si="36"/>
-        <v>836.33347555306909</v>
+        <f t="shared" si="43"/>
+        <v>540.35074405000796</v>
       </c>
       <c r="AS14" s="1">
-        <f t="shared" si="36"/>
-        <v>827.97014079753842</v>
+        <f t="shared" si="43"/>
+        <v>534.94723660950785</v>
       </c>
       <c r="AT14" s="1">
-        <f t="shared" si="36"/>
-        <v>819.69043938956304</v>
+        <f t="shared" si="43"/>
+        <v>529.59776424341283</v>
       </c>
       <c r="AU14" s="1">
-        <f t="shared" si="36"/>
-        <v>811.49353499566735</v>
+        <f t="shared" si="43"/>
+        <v>524.30178660097874</v>
       </c>
       <c r="AV14" s="1">
-        <f t="shared" si="36"/>
-        <v>803.37859964571066</v>
+        <f t="shared" si="43"/>
+        <v>519.05876873496891</v>
       </c>
       <c r="AW14" s="1">
-        <f t="shared" si="36"/>
-        <v>795.34481364925352</v>
+        <f t="shared" si="43"/>
+        <v>513.86818104761926</v>
       </c>
       <c r="AX14" s="1">
-        <f t="shared" si="36"/>
-        <v>787.39136551276101</v>
+        <f t="shared" si="43"/>
+        <v>508.72949923714305</v>
       </c>
       <c r="AY14" s="1">
-        <f t="shared" si="36"/>
-        <v>779.51745185763343</v>
+        <f t="shared" si="43"/>
+        <v>503.64220424477162</v>
       </c>
       <c r="AZ14" s="1">
-        <f t="shared" si="36"/>
-        <v>771.72227733905709</v>
+        <f t="shared" si="43"/>
+        <v>498.60578220232389</v>
       </c>
       <c r="BA14" s="1">
-        <f t="shared" si="36"/>
-        <v>764.00505456566646</v>
+        <f t="shared" si="43"/>
+        <v>493.61972438030062</v>
       </c>
       <c r="BB14" s="1">
-        <f t="shared" si="36"/>
-        <v>756.36500402000979</v>
+        <f t="shared" si="43"/>
+        <v>488.68352713649762</v>
       </c>
       <c r="BC14" s="1">
-        <f t="shared" si="36"/>
-        <v>748.80135397980973</v>
+        <f t="shared" si="43"/>
+        <v>483.79669186513263</v>
       </c>
       <c r="BD14" s="1">
-        <f t="shared" si="36"/>
-        <v>741.31334044001164</v>
+        <f t="shared" si="43"/>
+        <v>478.95872494648131</v>
       </c>
       <c r="BE14" s="1">
-        <f t="shared" si="36"/>
-        <v>733.90020703561152</v>
+        <f t="shared" si="43"/>
+        <v>474.16913769701648</v>
       </c>
       <c r="BF14" s="1">
-        <f t="shared" si="36"/>
-        <v>726.56120496525534</v>
+        <f t="shared" si="43"/>
+        <v>469.42744632004633</v>
       </c>
       <c r="BG14" s="1">
-        <f t="shared" si="36"/>
-        <v>719.29559291560281</v>
+        <f t="shared" si="43"/>
+        <v>464.73317185684584</v>
       </c>
       <c r="BH14" s="1">
-        <f t="shared" si="36"/>
-        <v>712.10263698644678</v>
+        <f t="shared" si="43"/>
+        <v>460.08584013827738</v>
       </c>
       <c r="BI14" s="1">
-        <f t="shared" si="36"/>
-        <v>704.98161061658232</v>
+        <f t="shared" si="43"/>
+        <v>455.48498173689461</v>
       </c>
       <c r="BJ14" s="1">
-        <f t="shared" si="36"/>
-        <v>697.93179451041647</v>
+        <f t="shared" si="43"/>
+        <v>450.93013191952565</v>
       </c>
       <c r="BK14" s="1">
-        <f t="shared" si="36"/>
-        <v>690.95247656531228</v>
+        <f t="shared" si="43"/>
+        <v>446.42083060033036</v>
       </c>
       <c r="BL14" s="1">
-        <f t="shared" si="36"/>
-        <v>684.04295179965914</v>
+        <f t="shared" si="43"/>
+        <v>441.95662229432708</v>
       </c>
       <c r="BM14" s="1">
-        <f t="shared" si="36"/>
-        <v>677.20252228166248</v>
+        <f t="shared" si="43"/>
+        <v>437.5370560713838</v>
       </c>
       <c r="BN14" s="1">
-        <f t="shared" si="36"/>
-        <v>670.43049705884584</v>
+        <f t="shared" si="43"/>
+        <v>433.16168551066994</v>
       </c>
       <c r="BO14" s="1">
-        <f t="shared" si="36"/>
-        <v>663.72619208825733</v>
+        <f t="shared" si="43"/>
+        <v>428.83006865556325</v>
       </c>
       <c r="BP14" s="1">
-        <f t="shared" si="36"/>
-        <v>657.08893016737477</v>
+        <f t="shared" si="43"/>
+        <v>424.54176796900759</v>
       </c>
       <c r="BQ14" s="1">
-        <f t="shared" si="36"/>
-        <v>650.51804086570098</v>
+        <f t="shared" si="43"/>
+        <v>420.2963502893175</v>
       </c>
       <c r="BR14" s="1">
-        <f t="shared" si="36"/>
-        <v>644.01286045704398</v>
+        <f t="shared" si="43"/>
+        <v>416.09338678642433</v>
       </c>
       <c r="BS14" s="1">
-        <f t="shared" si="36"/>
-        <v>637.57273185247357</v>
+        <f t="shared" si="43"/>
+        <v>411.9324529185601</v>
       </c>
       <c r="BT14" s="1">
-        <f t="shared" si="36"/>
-        <v>631.19700453394887</v>
+        <f t="shared" si="43"/>
+        <v>407.81312838937447</v>
       </c>
       <c r="BU14" s="1">
-        <f t="shared" si="36"/>
-        <v>624.88503448860934</v>
+        <f t="shared" si="43"/>
+        <v>403.73499710548072</v>
       </c>
       <c r="BV14" s="1">
-        <f t="shared" si="36"/>
-        <v>618.6361841437232</v>
+        <f t="shared" si="43"/>
+        <v>399.69764713442589</v>
       </c>
       <c r="BW14" s="1">
-        <f t="shared" si="36"/>
-        <v>612.44982230228595</v>
+        <f t="shared" si="43"/>
+        <v>395.70067066308161</v>
       </c>
       <c r="BX14" s="1">
-        <f t="shared" si="36"/>
-        <v>606.32532407926305</v>
+        <f t="shared" si="43"/>
+        <v>391.7436639564508</v>
       </c>
       <c r="BY14" s="1">
-        <f t="shared" si="36"/>
-        <v>600.26207083847044</v>
+        <f t="shared" si="43"/>
+        <v>387.82622731688627</v>
       </c>
       <c r="BZ14" s="1">
-        <f t="shared" si="36"/>
-        <v>594.25945013008572</v>
+        <f t="shared" si="43"/>
+        <v>383.94796504371743</v>
       </c>
       <c r="CA14" s="1">
-        <f t="shared" si="36"/>
-        <v>588.31685562878488</v>
+        <f t="shared" si="43"/>
+        <v>380.10848539328026</v>
       </c>
       <c r="CB14" s="1">
-        <f t="shared" si="36"/>
-        <v>582.43368707249704</v>
+        <f t="shared" si="43"/>
+        <v>376.30740053934744</v>
       </c>
       <c r="CC14" s="1">
-        <f t="shared" si="36"/>
-        <v>576.60935020177203</v>
+        <f t="shared" si="43"/>
+        <v>372.54432653395395</v>
       </c>
       <c r="CD14" s="1">
-        <f t="shared" si="36"/>
-        <v>570.84325669975431</v>
+        <f t="shared" si="43"/>
+        <v>368.8188832686144</v>
       </c>
       <c r="CE14" s="1">
-        <f t="shared" si="36"/>
-        <v>565.13482413275676</v>
+        <f t="shared" si="43"/>
+        <v>365.13069443592826</v>
       </c>
       <c r="CF14" s="1">
-        <f t="shared" si="36"/>
-        <v>559.48347589142918</v>
+        <f t="shared" si="43"/>
+        <v>361.47938749156896</v>
       </c>
       <c r="CG14" s="1">
-        <f t="shared" si="36"/>
-        <v>553.88864113251486</v>
+        <f t="shared" si="43"/>
+        <v>357.86459361665328</v>
       </c>
       <c r="CH14" s="1">
-        <f t="shared" si="36"/>
-        <v>548.3497547211897</v>
+        <f t="shared" si="43"/>
+        <v>354.28594768048674</v>
       </c>
       <c r="CI14" s="1">
-        <f t="shared" si="36"/>
-        <v>542.86625717397783</v>
+        <f t="shared" si="43"/>
+        <v>350.74308820368185</v>
       </c>
       <c r="CJ14" s="1">
-        <f t="shared" si="36"/>
-        <v>537.43759460223805</v>
+        <f t="shared" si="43"/>
+        <v>347.23565732164502</v>
       </c>
       <c r="CK14" s="1">
-        <f t="shared" si="36"/>
-        <v>532.06321865621567</v>
+        <f t="shared" si="43"/>
+        <v>343.76330074842855</v>
       </c>
       <c r="CL14" s="1">
-        <f t="shared" si="36"/>
-        <v>526.74258646965347</v>
+        <f t="shared" si="43"/>
+        <v>340.32566774094425</v>
       </c>
       <c r="CM14" s="1">
-        <f t="shared" si="36"/>
-        <v>521.47516060495695</v>
+        <f t="shared" si="43"/>
+        <v>336.92241106353481</v>
       </c>
       <c r="CN14" s="1">
-        <f t="shared" si="36"/>
-        <v>516.26040899890734</v>
+        <f t="shared" si="43"/>
+        <v>333.55318695289947</v>
       </c>
       <c r="CO14" s="1">
-        <f t="shared" si="36"/>
-        <v>511.09780490891825</v>
+        <f t="shared" si="43"/>
+        <v>330.21765508337046</v>
       </c>
       <c r="CP14" s="1">
-        <f t="shared" si="36"/>
-        <v>505.98682685982908</v>
+        <f t="shared" si="43"/>
+        <v>326.91547853253672</v>
       </c>
       <c r="CQ14" s="1">
-        <f t="shared" si="36"/>
-        <v>500.9269585912308</v>
+        <f t="shared" si="43"/>
+        <v>323.64632374721134</v>
       </c>
       <c r="CR14" s="1">
-        <f t="shared" si="36"/>
-        <v>495.91768900531849</v>
+        <f t="shared" si="43"/>
+        <v>320.40986050973925</v>
       </c>
       <c r="CS14" s="1">
-        <f t="shared" si="36"/>
-        <v>490.95851211526531</v>
+        <f t="shared" si="43"/>
+        <v>317.20576190464186</v>
       </c>
       <c r="CT14" s="1">
-        <f t="shared" si="36"/>
-        <v>486.04892699411266</v>
+        <f t="shared" si="43"/>
+        <v>314.03370428559543</v>
       </c>
       <c r="CU14" s="1">
-        <f t="shared" si="36"/>
-        <v>481.18843772417154</v>
+        <f t="shared" si="43"/>
+        <v>310.89336724273949</v>
       </c>
       <c r="CV14" s="1">
-        <f t="shared" si="36"/>
-        <v>476.37655334692982</v>
+        <f t="shared" si="43"/>
+        <v>307.7844335703121</v>
       </c>
       <c r="CW14" s="1">
-        <f t="shared" si="36"/>
-        <v>471.6127878134605</v>
+        <f t="shared" si="43"/>
+        <v>304.706589234609</v>
       </c>
       <c r="CX14" s="1">
-        <f t="shared" si="36"/>
-        <v>466.89665993532589</v>
+        <f t="shared" si="43"/>
+        <v>301.6595233422629</v>
       </c>
       <c r="CY14" s="1">
-        <f t="shared" si="36"/>
-        <v>462.22769333597262</v>
+        <f t="shared" si="43"/>
+        <v>298.64292810884029</v>
       </c>
       <c r="CZ14" s="1">
-        <f t="shared" si="36"/>
-        <v>457.60541640261289</v>
+        <f t="shared" si="43"/>
+        <v>295.65649882775188</v>
       </c>
       <c r="DA14" s="1">
-        <f t="shared" si="36"/>
-        <v>453.02936223858677</v>
+        <f t="shared" si="43"/>
+        <v>292.69993383947434</v>
       </c>
       <c r="DB14" s="1">
-        <f t="shared" ref="DB14:ER14" si="37">DA14*(1+$AQ$19)</f>
-        <v>448.49906861620087</v>
+        <f t="shared" si="43"/>
+        <v>289.77293450107959</v>
       </c>
       <c r="DC14" s="1">
-        <f t="shared" si="37"/>
-        <v>444.01407793003887</v>
+        <f t="shared" ref="DC14:ES14" si="44">DB14*(1+$AR$19)</f>
+        <v>286.87520515606877</v>
       </c>
       <c r="DD14" s="1">
-        <f t="shared" si="37"/>
-        <v>439.57393715073846</v>
+        <f t="shared" si="44"/>
+        <v>284.00645310450807</v>
       </c>
       <c r="DE14" s="1">
-        <f t="shared" si="37"/>
-        <v>435.17819777923108</v>
+        <f t="shared" si="44"/>
+        <v>281.166388573463</v>
       </c>
       <c r="DF14" s="1">
-        <f t="shared" si="37"/>
-        <v>430.82641580143877</v>
+        <f t="shared" si="44"/>
+        <v>278.35472468772838</v>
       </c>
       <c r="DG14" s="1">
-        <f t="shared" si="37"/>
-        <v>426.5181516434244</v>
+        <f t="shared" si="44"/>
+        <v>275.5711774408511</v>
       </c>
       <c r="DH14" s="1">
-        <f t="shared" si="37"/>
-        <v>422.25297012699014</v>
+        <f t="shared" si="44"/>
+        <v>272.81546566644261</v>
       </c>
       <c r="DI14" s="1">
-        <f t="shared" si="37"/>
-        <v>418.03044042572026</v>
+        <f t="shared" si="44"/>
+        <v>270.0873110097782</v>
       </c>
       <c r="DJ14" s="1">
-        <f t="shared" si="37"/>
-        <v>413.85013602146307</v>
+        <f t="shared" si="44"/>
+        <v>267.3864378996804</v>
       </c>
       <c r="DK14" s="1">
-        <f t="shared" si="37"/>
-        <v>409.71163466124841</v>
+        <f t="shared" si="44"/>
+        <v>264.71257352068358</v>
       </c>
       <c r="DL14" s="1">
-        <f t="shared" si="37"/>
-        <v>405.61451831463592</v>
+        <f t="shared" si="44"/>
+        <v>262.06544778547675</v>
       </c>
       <c r="DM14" s="1">
-        <f t="shared" si="37"/>
-        <v>401.55837313148953</v>
+        <f t="shared" si="44"/>
+        <v>259.44479330762198</v>
       </c>
       <c r="DN14" s="1">
-        <f t="shared" si="37"/>
-        <v>397.54278940017463</v>
+        <f t="shared" si="44"/>
+        <v>256.85034537454578</v>
       </c>
       <c r="DO14" s="1">
-        <f t="shared" si="37"/>
-        <v>393.56736150617286</v>
+        <f t="shared" si="44"/>
+        <v>254.28184192080033</v>
       </c>
       <c r="DP14" s="1">
-        <f t="shared" si="37"/>
-        <v>389.63168789111114</v>
+        <f t="shared" si="44"/>
+        <v>251.73902350159233</v>
       </c>
       <c r="DQ14" s="1">
-        <f t="shared" si="37"/>
-        <v>385.73537101220001</v>
+        <f t="shared" si="44"/>
+        <v>249.22163326657639</v>
       </c>
       <c r="DR14" s="1">
-        <f t="shared" si="37"/>
-        <v>381.87801730207798</v>
+        <f t="shared" si="44"/>
+        <v>246.72941693391061</v>
       </c>
       <c r="DS14" s="1">
-        <f t="shared" si="37"/>
-        <v>378.05923712905718</v>
+        <f t="shared" si="44"/>
+        <v>244.2621227645715</v>
       </c>
       <c r="DT14" s="1">
-        <f t="shared" si="37"/>
-        <v>374.27864475776659</v>
+        <f t="shared" si="44"/>
+        <v>241.81950153692577</v>
       </c>
       <c r="DU14" s="1">
-        <f t="shared" si="37"/>
-        <v>370.53585831018893</v>
+        <f t="shared" si="44"/>
+        <v>239.40130652155651</v>
       </c>
       <c r="DV14" s="1">
-        <f t="shared" si="37"/>
-        <v>366.83049972708704</v>
+        <f t="shared" si="44"/>
+        <v>237.00729345634093</v>
       </c>
       <c r="DW14" s="1">
-        <f t="shared" si="37"/>
-        <v>363.16219472981618</v>
+        <f t="shared" si="44"/>
+        <v>234.63722052177752</v>
       </c>
       <c r="DX14" s="1">
-        <f t="shared" si="37"/>
-        <v>359.53057278251799</v>
+        <f t="shared" si="44"/>
+        <v>232.29084831655973</v>
       </c>
       <c r="DY14" s="1">
-        <f t="shared" si="37"/>
-        <v>355.93526705469282</v>
+        <f t="shared" si="44"/>
+        <v>229.96793983339413</v>
       </c>
       <c r="DZ14" s="1">
-        <f t="shared" si="37"/>
-        <v>352.37591438414586</v>
+        <f t="shared" si="44"/>
+        <v>227.66826043506018</v>
       </c>
       <c r="EA14" s="1">
-        <f t="shared" si="37"/>
-        <v>348.8521552403044</v>
+        <f t="shared" si="44"/>
+        <v>225.39157783070956</v>
       </c>
       <c r="EB14" s="1">
-        <f t="shared" si="37"/>
-        <v>345.36363368790137</v>
+        <f t="shared" si="44"/>
+        <v>223.13766205240248</v>
       </c>
       <c r="EC14" s="1">
-        <f t="shared" si="37"/>
-        <v>341.90999735102235</v>
+        <f t="shared" si="44"/>
+        <v>220.90628543187844</v>
       </c>
       <c r="ED14" s="1">
-        <f t="shared" si="37"/>
-        <v>338.49089737751211</v>
+        <f t="shared" si="44"/>
+        <v>218.69722257755967</v>
       </c>
       <c r="EE14" s="1">
-        <f t="shared" si="37"/>
-        <v>335.105988403737</v>
+        <f t="shared" si="44"/>
+        <v>216.51025035178407</v>
       </c>
       <c r="EF14" s="1">
-        <f t="shared" si="37"/>
-        <v>331.7549285196996</v>
+        <f t="shared" si="44"/>
+        <v>214.34514784826624</v>
       </c>
       <c r="EG14" s="1">
-        <f t="shared" si="37"/>
-        <v>328.4373792345026</v>
+        <f t="shared" si="44"/>
+        <v>212.20169636978358</v>
       </c>
       <c r="EH14" s="1">
-        <f t="shared" si="37"/>
-        <v>325.15300544215756</v>
+        <f t="shared" si="44"/>
+        <v>210.07967940608575</v>
       </c>
       <c r="EI14" s="1">
-        <f t="shared" si="37"/>
-        <v>321.90147538773601</v>
+        <f t="shared" si="44"/>
+        <v>207.97888261202488</v>
       </c>
       <c r="EJ14" s="1">
-        <f t="shared" si="37"/>
-        <v>318.68246063385862</v>
+        <f t="shared" si="44"/>
+        <v>205.89909378590463</v>
       </c>
       <c r="EK14" s="1">
-        <f t="shared" si="37"/>
-        <v>315.49563602752005</v>
+        <f t="shared" si="44"/>
+        <v>203.84010284804558</v>
       </c>
       <c r="EL14" s="1">
-        <f t="shared" si="37"/>
-        <v>312.34067966724484</v>
+        <f t="shared" si="44"/>
+        <v>201.80170181956512</v>
       </c>
       <c r="EM14" s="1">
-        <f t="shared" si="37"/>
-        <v>309.2172728705724</v>
+        <f t="shared" si="44"/>
+        <v>199.78368480136947</v>
       </c>
       <c r="EN14" s="1">
-        <f t="shared" si="37"/>
-        <v>306.12510014186665</v>
+        <f t="shared" si="44"/>
+        <v>197.78584795335578</v>
       </c>
       <c r="EO14" s="1">
-        <f t="shared" si="37"/>
-        <v>303.06384914044799</v>
+        <f t="shared" si="44"/>
+        <v>195.80798947382223</v>
       </c>
       <c r="EP14" s="1">
-        <f t="shared" si="37"/>
-        <v>300.0332106490435</v>
+        <f t="shared" si="44"/>
+        <v>193.849909579084</v>
       </c>
       <c r="EQ14" s="1">
-        <f t="shared" si="37"/>
-        <v>297.03287854255308</v>
+        <f t="shared" si="44"/>
+        <v>191.91141048329317</v>
       </c>
       <c r="ER14" s="1">
-        <f t="shared" si="37"/>
-        <v>294.06254975712756</v>
+        <f t="shared" si="44"/>
+        <v>189.99229637846022</v>
+      </c>
+      <c r="ES14" s="1">
+        <f t="shared" si="44"/>
+        <v>188.09237341467562</v>
       </c>
     </row>
-    <row r="15" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>1</v>
       </c>
@@ -3167,20 +3212,20 @@
         <v>43.2</v>
       </c>
       <c r="S15" s="5">
-        <f>43.2</f>
-        <v>43.2</v>
+        <f>43.4</f>
+        <v>43.4</v>
       </c>
       <c r="T15" s="5">
-        <f t="shared" ref="T15:V15" si="38">43.2</f>
-        <v>43.2</v>
+        <f>43.4</f>
+        <v>43.4</v>
       </c>
       <c r="U15" s="5">
-        <f t="shared" si="38"/>
-        <v>43.2</v>
+        <f>43.4</f>
+        <v>43.4</v>
       </c>
       <c r="V15" s="5">
-        <f t="shared" si="38"/>
-        <v>43.2</v>
+        <f>43.4</f>
+        <v>43.4</v>
       </c>
       <c r="X15" s="5">
         <v>38.799999999999997</v>
@@ -3201,204 +3246,212 @@
         <v>42.6</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" ref="AD15:AN15" si="39">43.2</f>
+        <f t="shared" ref="AD15" si="45">43.2</f>
         <v>43.2</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" si="39"/>
-        <v>43.2</v>
+        <f t="shared" ref="AE15:AO15" si="46">43.4</f>
+        <v>43.4</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" si="39"/>
-        <v>43.2</v>
+        <f t="shared" si="46"/>
+        <v>43.4</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="39"/>
-        <v>43.2</v>
+        <f t="shared" si="46"/>
+        <v>43.4</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="39"/>
-        <v>43.2</v>
+        <f t="shared" si="46"/>
+        <v>43.4</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="39"/>
-        <v>43.2</v>
+        <f t="shared" si="46"/>
+        <v>43.4</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="39"/>
-        <v>43.2</v>
+        <f t="shared" si="46"/>
+        <v>43.4</v>
       </c>
       <c r="AK15" s="5">
-        <f t="shared" si="39"/>
-        <v>43.2</v>
+        <f t="shared" si="46"/>
+        <v>43.4</v>
       </c>
       <c r="AL15" s="5">
-        <f t="shared" si="39"/>
-        <v>43.2</v>
+        <f t="shared" si="46"/>
+        <v>43.4</v>
       </c>
       <c r="AM15" s="5">
-        <f t="shared" si="39"/>
-        <v>43.2</v>
+        <f t="shared" si="46"/>
+        <v>43.4</v>
       </c>
       <c r="AN15" s="5">
-        <f t="shared" si="39"/>
-        <v>43.2</v>
+        <f t="shared" si="46"/>
+        <v>43.4</v>
+      </c>
+      <c r="AO15" s="5">
+        <f t="shared" si="46"/>
+        <v>43.4</v>
       </c>
     </row>
-    <row r="16" spans="2:148" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="7">
-        <f t="shared" ref="C16:S16" si="40">C14/C15</f>
+        <f t="shared" ref="C16:S16" si="47">C14/C15</f>
         <v>-0.3152709359605918</v>
       </c>
       <c r="D16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>1.0120481927710845</v>
       </c>
       <c r="E16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>1.0263157894736845</v>
       </c>
       <c r="F16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>0.83732057416267758</v>
       </c>
       <c r="G16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>-0.53919239904988159</v>
       </c>
       <c r="H16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>1.1985815602836873</v>
       </c>
       <c r="I16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>-0.39386792452830199</v>
       </c>
       <c r="J16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>2.7223529411764749</v>
       </c>
       <c r="K16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>0.11529411764705841</v>
       </c>
       <c r="L16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>1.5680751173708916</v>
       </c>
       <c r="M16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>1.6323185011709589</v>
       </c>
       <c r="N16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>1.4707259953161611</v>
       </c>
       <c r="O16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>0.9533799533799544</v>
       </c>
       <c r="P16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>2.2372093023255832</v>
       </c>
       <c r="Q16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>2.3039443155452424</v>
       </c>
       <c r="R16" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="47"/>
         <v>1.1875000000000009</v>
       </c>
       <c r="S16" s="7">
-        <f t="shared" si="40"/>
-        <v>1.7418742592592589</v>
+        <f t="shared" si="47"/>
+        <v>1.5852534562211977</v>
       </c>
       <c r="T16" s="7">
-        <f t="shared" ref="T16" si="41">T14/T15</f>
-        <v>3.0015074074074071</v>
+        <f t="shared" ref="T16" si="48">T14/T15</f>
+        <v>2.4648516129032259</v>
       </c>
       <c r="U16" s="7">
-        <f t="shared" ref="U16" si="42">U14/U15</f>
-        <v>3.0902233333333324</v>
+        <f t="shared" ref="U16" si="49">U14/U15</f>
+        <v>2.4314886635944704</v>
       </c>
       <c r="V16" s="7">
-        <f t="shared" ref="V16" si="43">V14/V15</f>
-        <v>3.212477777777778</v>
+        <f t="shared" ref="V16" si="50">V14/V15</f>
+        <v>2.5109419354838716</v>
       </c>
       <c r="X16" s="7">
-        <f t="shared" ref="X16:AE16" si="44">X14/X15</f>
+        <f t="shared" ref="X16:AE16" si="51">X14/X15</f>
         <v>0.96391752577319501</v>
       </c>
       <c r="Y16" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v>0.62278481012657949</v>
       </c>
       <c r="Z16" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v>1.7786069651741292</v>
       </c>
       <c r="AA16" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v>2.5807228915662641</v>
       </c>
       <c r="AB16" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v>3.0023640661938562</v>
       </c>
       <c r="AC16" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v>4.7934272300469454</v>
       </c>
       <c r="AD16" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v>6.6597222222222285</v>
       </c>
       <c r="AE16" s="7">
-        <f t="shared" si="44"/>
-        <v>11.046082777777773</v>
+        <f t="shared" si="51"/>
+        <v>8.9925356682027697</v>
       </c>
       <c r="AF16" s="7">
-        <f t="shared" ref="AF16:AN16" si="45">AF14/AF15</f>
-        <v>13.677321542314813</v>
+        <f t="shared" ref="AF16:AN16" si="52">AF14/AF15</f>
+        <v>9.7071606237788046</v>
       </c>
       <c r="AG16" s="7">
-        <f t="shared" si="45"/>
-        <v>15.408590693385182</v>
+        <f t="shared" si="52"/>
+        <v>10.185254878805528</v>
       </c>
       <c r="AH16" s="7">
-        <f t="shared" si="45"/>
-        <v>16.550787559228521</v>
+        <f t="shared" si="52"/>
+        <v>10.489629090982564</v>
       </c>
       <c r="AI16" s="7">
-        <f t="shared" si="45"/>
-        <v>17.496900684471278</v>
+        <f t="shared" si="52"/>
+        <v>10.801223378534401</v>
       </c>
       <c r="AJ16" s="7">
-        <f t="shared" si="45"/>
-        <v>18.216618299665381</v>
+        <f t="shared" si="52"/>
+        <v>11.120197245879407</v>
       </c>
       <c r="AK16" s="7">
-        <f t="shared" si="45"/>
-        <v>18.684890237910931</v>
+        <f t="shared" si="52"/>
+        <v>11.446713651863407</v>
       </c>
       <c r="AL16" s="7">
-        <f t="shared" si="45"/>
-        <v>19.163678215082889</v>
+        <f t="shared" si="52"/>
+        <v>11.780939084890941</v>
       </c>
       <c r="AM16" s="7">
-        <f t="shared" si="45"/>
-        <v>19.653207394094576</v>
+        <f t="shared" si="52"/>
+        <v>12.123043639721514</v>
       </c>
       <c r="AN16" s="7">
-        <f t="shared" si="45"/>
-        <v>20.153707689622905</v>
+        <f t="shared" si="52"/>
+        <v>12.473201095968879</v>
+      </c>
+      <c r="AO16" s="7">
+        <f t="shared" ref="AO16" si="53">AO14/AO15</f>
+        <v>12.831588998342252</v>
       </c>
     </row>
-    <row r="18" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>39</v>
       </c>
@@ -3407,295 +3460,303 @@
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10">
-        <f t="shared" ref="G18:R18" si="46">G3/C3-1</f>
+        <f t="shared" ref="G18:R18" si="54">G3/C3-1</f>
         <v>6.2468765617191391E-2</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.11941391941391943</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.11524780649751021</v>
       </c>
       <c r="J18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>6.1937184274105439E-2</v>
       </c>
       <c r="K18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.12935089369708375</v>
       </c>
       <c r="L18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.10143979057591634</v>
       </c>
       <c r="M18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.10737826918987858</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.1048603929679417</v>
       </c>
       <c r="O18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.14764681382757194</v>
       </c>
       <c r="P18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.16300257476728075</v>
       </c>
       <c r="Q18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.17780337941628277</v>
       </c>
       <c r="R18" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.22351179333582927</v>
       </c>
       <c r="S18" s="10">
-        <f t="shared" ref="S18:V18" si="47">S3/O3-1</f>
-        <v>0.21999999999999997</v>
+        <f t="shared" ref="S18:V18" si="55">S3/O3-1</f>
+        <v>0.12665577935038996</v>
       </c>
       <c r="T18" s="10">
-        <f t="shared" si="47"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="55"/>
+        <v>7.2888283378746532E-2</v>
       </c>
       <c r="U18" s="10">
-        <f t="shared" si="47"/>
-        <v>0.17999999999999994</v>
+        <f t="shared" si="55"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="V18" s="10">
-        <f t="shared" si="47"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="55"/>
+        <v>0</v>
       </c>
       <c r="X18" s="10"/>
       <c r="Y18" s="10">
-        <f t="shared" ref="Y18:AN18" si="48">Y3/X3-1</f>
+        <f t="shared" ref="Y18:AO18" si="56">Y3/X3-1</f>
         <v>2.4611143925969747E-2</v>
       </c>
       <c r="Z18" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.47655649500384323</v>
       </c>
       <c r="AA18" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>9.7540343571056898E-2</v>
       </c>
       <c r="AB18" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>8.9346060354538404E-2</v>
       </c>
       <c r="AC18" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.1103189289213018</v>
       </c>
       <c r="AD18" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.17901083280231367</v>
       </c>
       <c r="AE18" s="10">
-        <f t="shared" si="48"/>
-        <v>0.18589531451378183</v>
+        <f t="shared" si="56"/>
+        <v>5.4463892237974543E-2</v>
       </c>
       <c r="AF18" s="10">
-        <f t="shared" si="48"/>
-        <v>0.12999999999999989</v>
+        <f t="shared" si="56"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AG18" s="10">
-        <f t="shared" si="48"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="56"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH18" s="10">
-        <f t="shared" si="48"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="56"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI18" s="10">
-        <f t="shared" si="48"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="56"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ18" s="10">
-        <f t="shared" si="48"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="56"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK18" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL18" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM18" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN18" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>2.0000000000000018E-2</v>
       </c>
+      <c r="AO18" s="10">
+        <f t="shared" si="56"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
     </row>
-    <row r="19" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="10">
-        <f t="shared" ref="C19:R19" si="49">C5/C3</f>
+        <f t="shared" ref="C19:R19" si="57">C5/C3</f>
         <v>0.31584207896051969</v>
       </c>
       <c r="D19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.36019536019536019</v>
       </c>
       <c r="E19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.36708560588095807</v>
       </c>
       <c r="F19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.36854820997144727</v>
       </c>
       <c r="G19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.30503292568203194</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.3710732984293193</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.37274080374229218</v>
       </c>
       <c r="J19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.35573940020682548</v>
       </c>
       <c r="K19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.36005830903790081</v>
       </c>
       <c r="L19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.39849475143592789</v>
       </c>
       <c r="M19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.38652073732718889</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.35230250842381144</v>
       </c>
       <c r="O19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.39176193068408643</v>
       </c>
       <c r="P19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.40837874659400553</v>
       </c>
       <c r="Q19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.40642321486794908</v>
       </c>
       <c r="R19" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.36551407588739293</v>
       </c>
       <c r="S19" s="10">
-        <f t="shared" ref="S19:V19" si="50">S5/S3</f>
+        <f t="shared" ref="S19:V19" si="58">S5/S3</f>
+        <v>0.38991786116927035</v>
+      </c>
+      <c r="T19" s="10">
+        <f t="shared" si="58"/>
         <v>0.4</v>
       </c>
-      <c r="T19" s="10">
-        <f t="shared" si="50"/>
+      <c r="U19" s="10">
+        <f t="shared" si="58"/>
         <v>0.4</v>
       </c>
-      <c r="U19" s="10">
-        <f t="shared" si="50"/>
-        <v>0.4</v>
-      </c>
       <c r="V19" s="10">
-        <f t="shared" si="50"/>
-        <v>0.4</v>
+        <f t="shared" si="58"/>
+        <v>0.39999999999999997</v>
       </c>
       <c r="X19" s="10">
-        <f t="shared" ref="X19:AN19" si="51">X5/X3</f>
+        <f t="shared" ref="X19:AN19" si="59">X5/X3</f>
         <v>0.34691868478046861</v>
       </c>
       <c r="Y19" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.33397386625672554</v>
       </c>
       <c r="Z19" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.3480609057782405</v>
       </c>
       <c r="AA19" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.35364913736882669</v>
       </c>
       <c r="AB19" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.35218243169696317</v>
       </c>
       <c r="AC19" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.37429537767756482</v>
       </c>
       <c r="AD19" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.39242506132291199</v>
       </c>
       <c r="AE19" s="10">
-        <f t="shared" si="51"/>
-        <v>0.39999999999999997</v>
+        <f t="shared" si="59"/>
+        <v>0.39753183966262701</v>
       </c>
       <c r="AF19" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.41</v>
       </c>
       <c r="AG19" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.41</v>
       </c>
       <c r="AH19" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.41</v>
       </c>
       <c r="AI19" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
+        <v>0.41000000000000003</v>
+      </c>
+      <c r="AJ19" s="10">
+        <f t="shared" si="59"/>
         <v>0.41</v>
       </c>
-      <c r="AJ19" s="10">
-        <f t="shared" si="51"/>
+      <c r="AK19" s="10">
+        <f t="shared" si="59"/>
+        <v>0.40999999999999992</v>
+      </c>
+      <c r="AL19" s="10">
+        <f t="shared" si="59"/>
         <v>0.41</v>
       </c>
-      <c r="AK19" s="10">
-        <f t="shared" si="51"/>
+      <c r="AM19" s="10">
+        <f t="shared" si="59"/>
         <v>0.41</v>
       </c>
-      <c r="AL19" s="10">
-        <f t="shared" si="51"/>
+      <c r="AN19" s="10">
+        <f t="shared" si="59"/>
         <v>0.41</v>
       </c>
-      <c r="AM19" s="10">
-        <f t="shared" si="51"/>
+      <c r="AO19" s="10">
+        <f t="shared" ref="AO19" si="60">AO5/AO3</f>
         <v>0.41</v>
       </c>
-      <c r="AN19" s="10">
-        <f t="shared" si="51"/>
-        <v>0.41</v>
-      </c>
-      <c r="AP19" t="s">
+      <c r="AQ19" t="s">
         <v>44</v>
       </c>
-      <c r="AQ19" s="10">
+      <c r="AR19" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="20" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>41</v>
       </c>
@@ -3704,359 +3765,367 @@
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10">
-        <f t="shared" ref="G20:R20" si="52">G6/C6-1</f>
+        <f t="shared" ref="G20:R20" si="61">G6/C6-1</f>
         <v>0.18740629685157417</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>0.1258278145695364</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>0.86093418259023369</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>-0.62253289473684215</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>7.0707070707070718E-2</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>0.14607843137254917</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>-0.35539075869937253</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>1.4945533769063184</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>-6.4858490566037652E-3</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>-1.7964071856287456E-2</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>4.8672566371681381E-2</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>7.0742358078602408E-2</v>
       </c>
       <c r="S20" s="10">
-        <f t="shared" ref="S20:V20" si="53">S6/O6-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="S20:V20" si="62">S6/O6-1</f>
+        <v>2.7299703264094921E-2</v>
       </c>
       <c r="T20" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="U20" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="V20" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X20" s="10"/>
       <c r="Y20" s="10">
-        <f t="shared" ref="Y20:AN20" si="54">Y6/X6-1</f>
+        <f t="shared" ref="Y20:AO20" si="63">Y6/X6-1</f>
         <v>2.7053455019556694E-2</v>
       </c>
       <c r="Z20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>0.34687400825134862</v>
       </c>
       <c r="AA20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>3.6286522148916145E-2</v>
       </c>
       <c r="AB20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>9.5043201455206949E-2</v>
       </c>
       <c r="AC20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>6.7275747508305672E-2</v>
       </c>
       <c r="AD20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>2.0233463035019383E-2</v>
       </c>
       <c r="AE20" s="10">
-        <f t="shared" si="54"/>
-        <v>3.1828756674294523E-2</v>
+        <f t="shared" si="63"/>
+        <v>2.4534706331045042E-2</v>
       </c>
       <c r="AF20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN20" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP20" t="s">
+      <c r="AO20" s="10">
+        <f t="shared" si="63"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AQ20" t="s">
         <v>45</v>
       </c>
-      <c r="AQ20" s="10">
+      <c r="AR20" s="10">
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="10">
-        <f t="shared" ref="C21:R21" si="55">C8/C3</f>
+        <f t="shared" ref="C21:R21" si="64">C8/C3</f>
         <v>-1.7491254372813663E-2</v>
       </c>
       <c r="D21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.13894993894993896</v>
       </c>
       <c r="E21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.14370405501541383</v>
       </c>
       <c r="F21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.10147155721502291</v>
       </c>
       <c r="G21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>-6.7497648165569191E-2</v>
       </c>
       <c r="H21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.14856020942408371</v>
       </c>
       <c r="I21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.26080661840744596</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>6.872136609745904E-3</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.1669637551990493</v>
       </c>
       <c r="M21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.16954685099846384</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.13796330962186459</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>8.6009798584648939E-2</v>
       </c>
       <c r="P21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.21287465940054506</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.21323769155526567</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>8.6903304773561868E-2</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" ref="S21:V21" si="56">S8/S3</f>
-        <v>0.13685267319310707</v>
+        <f t="shared" ref="S21:V21" si="65">S8/S3</f>
+        <v>0.11112900628120466</v>
       </c>
       <c r="T21" s="10">
-        <f t="shared" si="56"/>
-        <v>0.23219232515894642</v>
+        <f t="shared" si="65"/>
+        <v>0.21231111111111112</v>
       </c>
       <c r="U21" s="10">
-        <f t="shared" si="56"/>
-        <v>0.233009123916155</v>
+        <f t="shared" si="65"/>
+        <v>0.20869006429229414</v>
       </c>
       <c r="V21" s="10">
-        <f t="shared" si="56"/>
-        <v>0.23362780054281307</v>
+        <f t="shared" si="65"/>
+        <v>0.20867197062423501</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" ref="X21:AN21" si="57">X8/X3</f>
+        <f t="shared" ref="X21:AN21" si="66">X8/X3</f>
         <v>4.4890726520968663E-2</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="66"/>
         <v>3.1225980015372683E-2</v>
       </c>
       <c r="Z21" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="66"/>
         <v>7.1902654867256638E-2</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="66"/>
         <v>9.2903302306278523E-2</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="66"/>
         <v>9.0072929139000821E-2</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="66"/>
         <v>0.12234694377726578</v>
       </c>
       <c r="AD21" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="66"/>
         <v>0.14966947989855747</v>
       </c>
       <c r="AE21" s="10">
-        <f t="shared" si="57"/>
-        <v>0.21030551451847784</v>
+        <f t="shared" si="66"/>
+        <v>0.18570138729536162</v>
       </c>
       <c r="AF21" s="10">
-        <f t="shared" si="57"/>
-        <v>0.23877134938836056</v>
+        <f t="shared" si="66"/>
+        <v>0.20224321017825894</v>
       </c>
       <c r="AG21" s="10">
-        <f t="shared" si="57"/>
-        <v>0.24986950266874461</v>
+        <f t="shared" si="66"/>
+        <v>0.20627732260198203</v>
       </c>
       <c r="AH21" s="10">
-        <f t="shared" si="57"/>
-        <v>0.2559697120908877</v>
+        <f t="shared" si="66"/>
+        <v>0.20827460375294304</v>
       </c>
       <c r="AI21" s="10">
-        <f t="shared" si="57"/>
-        <v>0.26041289347288132</v>
+        <f t="shared" si="66"/>
+        <v>0.2102523037161495</v>
       </c>
       <c r="AJ21" s="10">
-        <f t="shared" si="57"/>
-        <v>0.26331749748311656</v>
+        <f t="shared" si="66"/>
+        <v>0.21221061446403036</v>
       </c>
       <c r="AK21" s="10">
-        <f t="shared" si="57"/>
-        <v>0.26475556123328214</v>
+        <f t="shared" si="66"/>
+        <v>0.21414972608693195</v>
       </c>
       <c r="AL21" s="10">
-        <f t="shared" si="57"/>
-        <v>0.26617952631923031</v>
+        <f t="shared" si="66"/>
+        <v>0.21606982681156991</v>
       </c>
       <c r="AM21" s="10">
-        <f t="shared" si="57"/>
-        <v>0.26758953096315952</v>
+        <f t="shared" si="66"/>
+        <v>0.21797110301929964</v>
       </c>
       <c r="AN21" s="10">
-        <f t="shared" si="57"/>
-        <v>0.26898571203214805</v>
-      </c>
-      <c r="AP21" t="s">
+        <f t="shared" si="66"/>
+        <v>0.21985373926420848</v>
+      </c>
+      <c r="AO21" s="10">
+        <f t="shared" ref="AO21" si="67">AO8/AO3</f>
+        <v>0.22171791829102996</v>
+      </c>
+      <c r="AQ21" t="s">
         <v>46</v>
       </c>
-      <c r="AQ21" s="5">
-        <f>NPV(AQ20,AE14:ER14)</f>
-        <v>8172.6368556960624</v>
+      <c r="AR21" s="5">
+        <f>NPV(AR20,AE14:ES14)</f>
+        <v>5320.5072974069917</v>
       </c>
     </row>
-    <row r="22" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="10">
-        <f t="shared" ref="C22" si="58">C12/C11</f>
+        <f t="shared" ref="C22" si="68">C12/C11</f>
         <v>0.18124999999999966</v>
       </c>
       <c r="D22" s="10">
-        <f t="shared" ref="D22:M22" si="59">D12/D11</f>
+        <f t="shared" ref="D22:M22" si="69">D12/D11</f>
         <v>0.2699490662139219</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>0.28449744463373078</v>
       </c>
       <c r="F22" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>0.22857142857142898</v>
       </c>
       <c r="G22" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>0.25252525252525237</v>
       </c>
       <c r="H22" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>0.27000000000000007</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>8.1250000000000018</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>0.11085450346420307</v>
       </c>
       <c r="K22" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>0.23437500000000064</v>
       </c>
       <c r="L22" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="M22" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>0.26388888888888901</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" ref="N22:O22" si="60">N12/N11</f>
+        <f t="shared" ref="N22:O22" si="70">N12/N11</f>
         <v>0.20405576679340914</v>
       </c>
       <c r="O22" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>0.21003717472118946</v>
       </c>
       <c r="P22" s="10">
-        <f t="shared" ref="P22" si="61">P12/P11</f>
+        <f t="shared" ref="P22" si="71">P12/P11</f>
         <v>0.25771604938271586</v>
       </c>
       <c r="Q22" s="10">
@@ -4068,39 +4137,39 @@
         <v>0.20062208398133735</v>
       </c>
       <c r="S22" s="10">
-        <f t="shared" ref="S22:V22" si="62">S12/S11</f>
+        <f t="shared" ref="S22:V22" si="72">S12/S11</f>
+        <v>0.17391304347826092</v>
+      </c>
+      <c r="T22" s="10">
+        <f t="shared" si="72"/>
         <v>0.23999999999999996</v>
       </c>
-      <c r="T22" s="10">
-        <f t="shared" si="62"/>
-        <v>0.24000000000000002</v>
-      </c>
       <c r="U22" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>0.24</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" si="62"/>
-        <v>0.24000000000000002</v>
+        <f t="shared" si="72"/>
+        <v>0.24</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" ref="X22:AB22" si="63">X12/X11</f>
+        <f t="shared" ref="X22:AB22" si="73">X12/X11</f>
         <v>0.21649484536082489</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="73"/>
         <v>0.25373134328358293</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="73"/>
         <v>0.25708289611752361</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="73"/>
         <v>0.2726036709721279</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="73"/>
         <v>0.26245654692931614</v>
       </c>
       <c r="AC22" s="10">
@@ -4108,115 +4177,119 @@
         <v>0.24094135225999264</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" ref="AD22:AN22" si="64">AD12/AD11</f>
+        <f t="shared" ref="AD22:AN22" si="74">AD12/AD11</f>
         <v>0.2430174889062906</v>
       </c>
       <c r="AE22" s="10">
-        <f t="shared" si="64"/>
-        <v>0.24000000000000007</v>
+        <f t="shared" si="74"/>
+        <v>0.229181383438501</v>
       </c>
       <c r="AF22" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.25</v>
       </c>
       <c r="AG22" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.25</v>
       </c>
       <c r="AH22" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.25</v>
       </c>
       <c r="AI22" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.25</v>
       </c>
       <c r="AJ22" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.25</v>
       </c>
       <c r="AK22" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.25</v>
       </c>
       <c r="AL22" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.25</v>
       </c>
       <c r="AM22" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.25</v>
       </c>
       <c r="AN22" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.25</v>
       </c>
-      <c r="AP22" t="s">
+      <c r="AO22" s="10">
+        <f t="shared" ref="AO22" si="75">AO12/AO11</f>
+        <v>0.25</v>
+      </c>
+      <c r="AQ22" t="s">
         <v>47</v>
       </c>
-      <c r="AQ22" s="5">
+      <c r="AR22" s="5">
         <f>Main!D8</f>
-        <v>569</v>
+        <v>298.2999999999999</v>
       </c>
     </row>
-    <row r="23" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="10">
-        <f t="shared" ref="C23" si="65">C13/C11</f>
+        <f t="shared" ref="C23" si="76">C13/C11</f>
         <v>1.8749999999999965E-2</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" ref="D23:M23" si="66">D13/D11</f>
+        <f t="shared" ref="D23:M23" si="77">D13/D11</f>
         <v>1.6977928692699488E-2</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>-1.533219761499148E-2</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>2.1978021978022021E-3</v>
       </c>
       <c r="G23" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>-1.6835016835016824E-2</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>5.7142857142857169E-3</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>-0.16666666666666671</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>-1.5396458814472655E-3</v>
       </c>
       <c r="K23" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>-2.2522522522522527E-3</v>
       </c>
       <c r="M23" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>-8.5470085470085513E-3</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" ref="N23:O23" si="67">N13/N11</f>
+        <f t="shared" ref="N23:O23" si="78">N13/N11</f>
         <v>7.0356338696144198E-19</v>
       </c>
       <c r="O23" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="78"/>
         <v>2.9739776951672844E-2</v>
       </c>
       <c r="P23" s="10">
-        <f t="shared" ref="P23" si="68">P13/P11</f>
+        <f t="shared" ref="P23" si="79">P13/P11</f>
         <v>0</v>
       </c>
       <c r="Q23" s="10">
@@ -4228,39 +4301,39 @@
         <v>1.5552099533437005E-3</v>
       </c>
       <c r="S23" s="10">
-        <f t="shared" ref="S23:V23" si="69">S13/S11</f>
+        <f t="shared" ref="S23:V23" si="80">S13/S11</f>
+        <v>-4.8309178743961368E-3</v>
+      </c>
+      <c r="T23" s="10">
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
-      <c r="T23" s="10">
-        <f t="shared" si="69"/>
+      <c r="U23" s="10">
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
-      <c r="U23" s="10">
-        <f t="shared" si="69"/>
+      <c r="V23" s="10">
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
-      <c r="V23" s="10">
-        <f t="shared" si="69"/>
-        <v>0</v>
-      </c>
       <c r="X23" s="10">
-        <f t="shared" ref="X23:AB23" si="70">X13/X11</f>
+        <f t="shared" ref="X23:AB23" si="81">X13/X11</f>
         <v>1.2371134020618565E-2</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="81"/>
         <v>1.1940298507462728E-2</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="81"/>
         <v>-7.3452256033578172E-3</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="81"/>
         <v>-6.7980965329707699E-4</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="81"/>
         <v>1.7381228273464647E-3</v>
       </c>
       <c r="AC23" s="10">
@@ -4268,241 +4341,249 @@
         <v>-3.735524841240196E-3</v>
       </c>
       <c r="AD23" s="10">
-        <f t="shared" ref="AD23:AN23" si="71">AD13/AD11</f>
+        <f t="shared" ref="AD23:AN23" si="82">AD13/AD11</f>
         <v>6.0036543983294135E-3</v>
       </c>
       <c r="AE23" s="10">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <f t="shared" si="82"/>
+        <v>-7.908345439692141E-4</v>
       </c>
       <c r="AF23" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="82"/>
         <v>0.01</v>
       </c>
       <c r="AG23" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="82"/>
         <v>0.01</v>
       </c>
       <c r="AH23" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="82"/>
         <v>0.01</v>
       </c>
       <c r="AI23" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="82"/>
         <v>0.01</v>
       </c>
       <c r="AJ23" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="82"/>
         <v>0.01</v>
       </c>
       <c r="AK23" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="82"/>
         <v>0.01</v>
       </c>
       <c r="AL23" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="82"/>
         <v>0.01</v>
       </c>
       <c r="AM23" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="82"/>
         <v>0.01</v>
       </c>
       <c r="AN23" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="82"/>
         <v>0.01</v>
       </c>
-      <c r="AP23" t="s">
+      <c r="AO23" s="10">
+        <f t="shared" ref="AO23" si="83">AO13/AO11</f>
+        <v>0.01</v>
+      </c>
+      <c r="AQ23" t="s">
         <v>48</v>
       </c>
-      <c r="AQ23" s="5">
-        <f>AQ21+AQ22</f>
-        <v>8741.6368556960624</v>
+      <c r="AR23" s="5">
+        <f>AR21+AR22</f>
+        <v>5618.8072974069919</v>
       </c>
     </row>
-    <row r="24" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="10">
-        <f t="shared" ref="C24:R24" si="72">C14/C3</f>
+        <f t="shared" ref="C24:R24" si="84">C14/C3</f>
         <v>-3.1984007996002067E-2</v>
       </c>
       <c r="D24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>0.10256410256410259</v>
       </c>
       <c r="E24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>0.10173108845150584</v>
       </c>
       <c r="F24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>7.687239182956275E-2</v>
       </c>
       <c r="G24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>-5.3386641580432777E-2</v>
       </c>
       <c r="H24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>0.11060209424083764</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>-3.5509249415266855E-2</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>0.23929679420889377</v>
       </c>
       <c r="K24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>1.0204081632653026E-2</v>
       </c>
       <c r="L24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>0.13230342642107346</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>0.13383256528417808</v>
       </c>
       <c r="N24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>0.11755896667914653</v>
       </c>
       <c r="O24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>7.4215205951732963E-2</v>
       </c>
       <c r="P24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>0.1638283378746595</v>
       </c>
       <c r="Q24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>0.16188457776328652</v>
       </c>
       <c r="R24" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>7.8488372093023312E-2</v>
       </c>
       <c r="S24" s="10">
-        <f t="shared" ref="S24:V24" si="73">S14/S3</f>
-        <v>0.11192067132501017</v>
+        <f t="shared" ref="S24:V24" si="85">S14/S3</f>
+        <v>0.11080689321952003</v>
       </c>
       <c r="T24" s="10">
-        <f t="shared" si="73"/>
-        <v>0.18401612170753862</v>
+        <f t="shared" si="85"/>
+        <v>0.16980088888888889</v>
       </c>
       <c r="U24" s="10">
-        <f t="shared" si="73"/>
-        <v>0.18443690903162699</v>
+        <f t="shared" si="85"/>
+        <v>0.16702480840516493</v>
       </c>
       <c r="V24" s="10">
-        <f t="shared" si="73"/>
-        <v>0.18463498483316482</v>
+        <f t="shared" si="85"/>
+        <v>0.16673023255813954</v>
       </c>
       <c r="X24" s="10">
-        <f t="shared" ref="X24:AN24" si="74">X14/X3</f>
+        <f t="shared" ref="X24:AN24" si="86">X14/X3</f>
         <v>3.6818271313250606E-2</v>
       </c>
       <c r="Y24" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>2.3635664873174374E-2</v>
       </c>
       <c r="Z24" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>4.6525247267048417E-2</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>6.349676883856048E-2</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>6.9119407858931156E-2</v>
       </c>
       <c r="AC24" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>0.10009313268957398</v>
       </c>
       <c r="AD24" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>0.11961085935226386</v>
       </c>
       <c r="AE24" s="10">
-        <f t="shared" si="74"/>
-        <v>0.16729248634674801</v>
+        <f t="shared" si="86"/>
+        <v>0.15387601634190259</v>
       </c>
       <c r="AF24" s="10">
-        <f t="shared" si="74"/>
-        <v>0.18331194094066078</v>
+        <f t="shared" si="86"/>
+        <v>0.15971571203938772</v>
       </c>
       <c r="AG24" s="10">
-        <f t="shared" si="74"/>
-        <v>0.19121803999808595</v>
+        <f t="shared" si="86"/>
+        <v>0.16270095523294276</v>
       </c>
       <c r="AH24" s="10">
-        <f t="shared" si="74"/>
-        <v>0.19561191672241063</v>
+        <f t="shared" si="86"/>
+        <v>0.16427752893668801</v>
       </c>
       <c r="AI24" s="10">
-        <f t="shared" si="74"/>
-        <v>0.19884031008186323</v>
+        <f t="shared" si="86"/>
+        <v>0.16584057908749519</v>
       </c>
       <c r="AJ24" s="10">
-        <f t="shared" si="74"/>
-        <v>0.20098971704943736</v>
+        <f t="shared" si="86"/>
+        <v>0.16739025722070691</v>
       </c>
       <c r="AK24" s="10">
-        <f t="shared" si="74"/>
-        <v>0.20211402901781411</v>
+        <f t="shared" si="86"/>
+        <v>0.16892671357182396</v>
       </c>
       <c r="AL24" s="10">
-        <f t="shared" si="74"/>
-        <v>0.20322849762950579</v>
+        <f t="shared" si="86"/>
+        <v>0.17045009709107065</v>
       </c>
       <c r="AM24" s="10">
-        <f t="shared" si="74"/>
-        <v>0.20433323094986899</v>
+        <f t="shared" si="86"/>
+        <v>0.1719605554578349</v>
       </c>
       <c r="AN24" s="10">
-        <f t="shared" si="74"/>
-        <v>0.20542833609814737</v>
-      </c>
-      <c r="AP24" t="s">
+        <f t="shared" si="86"/>
+        <v>0.17345823509498456</v>
+      </c>
+      <c r="AO24" s="10">
+        <f t="shared" ref="AO24" si="87">AO14/AO3</f>
+        <v>0.1749432811830626</v>
+      </c>
+      <c r="AQ24" t="s">
         <v>49</v>
       </c>
-      <c r="AQ24" s="4">
-        <f>AQ23/AN15</f>
-        <v>202.35270499296439</v>
+      <c r="AR24" s="4">
+        <f>AR23/AN15</f>
+        <v>129.46560593103669</v>
       </c>
     </row>
-    <row r="25" spans="2:43" x14ac:dyDescent="0.3">
-      <c r="AP25" t="s">
+    <row r="25" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="AQ25" t="s">
         <v>50</v>
       </c>
-      <c r="AQ25" s="4">
+      <c r="AR25" s="4">
         <f>Main!D3</f>
-        <v>140.65</v>
+        <v>70.83</v>
       </c>
     </row>
-    <row r="26" spans="2:43" x14ac:dyDescent="0.3">
-      <c r="AP26" s="1" t="s">
+    <row r="26" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="AQ26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AQ26" s="12">
-        <f>AQ24/AQ25-1</f>
-        <v>0.43869680051876569</v>
+      <c r="AR26" s="12">
+        <f>AR24/AR25-1</f>
+        <v>0.82783574659094583</v>
       </c>
     </row>
-    <row r="27" spans="2:43" x14ac:dyDescent="0.3">
-      <c r="AP27" t="s">
+    <row r="27" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="AQ27" t="s">
         <v>52</v>
       </c>
-      <c r="AQ27" s="6" t="s">
-        <v>59</v>
+      <c r="AR27" s="6" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/LRN.xlsx
+++ b/Financial Analysis/LRN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAA247C-B5F5-491E-A042-253906D3A93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46810312-B933-4832-9D64-3111D61D7877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7397855C-6173-4C21-9C59-A8371E1F4110}"/>
   </bookViews>
@@ -236,7 +236,7 @@
     <t>Q426</t>
   </si>
   <si>
-    <t>Heavily undervalued</t>
+    <t>Undervalued</t>
   </si>
 </sst>
 </file>
@@ -351,13 +351,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -375,7 +375,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13975080" y="7620"/>
+          <a:off x="14698980" y="7620"/>
           <a:ext cx="0" cy="6316980"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -774,17 +774,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>70.83</v>
+        <v>81.36</v>
       </c>
       <c r="E3" s="3">
-        <v>45960</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45961</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="3">
-        <v>46049</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -805,7 +805,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>3074.0219999999999</v>
+        <v>3531.0239999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -813,11 +813,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="5">
-        <f>518.4+196.7</f>
-        <v>715.09999999999991</v>
+        <f>497.1+128.6</f>
+        <v>625.70000000000005</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -825,11 +825,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="5">
-        <f>416.8</f>
-        <v>416.8</v>
+        <f>417.2</f>
+        <v>417.2</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -838,7 +838,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>298.2999999999999</v>
+        <v>208.50000000000006</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,7 +847,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>2775.7220000000002</v>
+        <v>3322.5239999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
         <v>620.9</v>
       </c>
       <c r="T3" s="8">
-        <v>630</v>
+        <v>631.29999999999995</v>
       </c>
       <c r="U3" s="8">
         <f>Q3*1.03</f>
@@ -1194,47 +1194,47 @@
       </c>
       <c r="AE3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>2536.3020000000001</v>
+        <v>2537.6019999999999</v>
       </c>
       <c r="AF3" s="8">
         <f>AE3*1.04</f>
-        <v>2637.7540800000002</v>
+        <v>2639.10608</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.03</f>
-        <v>2716.8867024000001</v>
+        <v>2718.2792623999999</v>
       </c>
       <c r="AH3" s="8">
         <f>AG3*1.02</f>
-        <v>2771.2244364480002</v>
+        <v>2772.644847648</v>
       </c>
       <c r="AI3" s="8">
         <f>AH3*1.02</f>
-        <v>2826.6489251769603</v>
+        <v>2828.0977446009601</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.02</f>
-        <v>2883.1819036804995</v>
+        <v>2884.6596994929796</v>
       </c>
       <c r="AK3" s="8">
-        <f t="shared" ref="AK3:AO3" si="0">AJ3*1.02</f>
-        <v>2940.8455417541095</v>
+        <f>AJ3*1.01</f>
+        <v>2913.5062964879094</v>
       </c>
       <c r="AL3" s="8">
-        <f t="shared" si="0"/>
-        <v>2999.6624525891916</v>
+        <f t="shared" ref="AL3:AO3" si="0">AK3*1.01</f>
+        <v>2942.6413594527885</v>
       </c>
       <c r="AM3" s="8">
         <f t="shared" si="0"/>
-        <v>3059.6557016409756</v>
+        <v>2972.0677730473162</v>
       </c>
       <c r="AN3" s="8">
         <f t="shared" si="0"/>
-        <v>3120.8488156737953</v>
+        <v>3001.7884507777894</v>
       </c>
       <c r="AO3" s="8">
         <f t="shared" si="0"/>
-        <v>3183.2657919872713</v>
+        <v>3031.8063352855675</v>
       </c>
     </row>
     <row r="4" spans="2:149" x14ac:dyDescent="0.3">
@@ -1296,11 +1296,10 @@
         <v>378.8</v>
       </c>
       <c r="T4" s="5">
-        <f t="shared" ref="T4:V4" si="1">T3-T5</f>
-        <v>378</v>
+        <v>371.6</v>
       </c>
       <c r="U4" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="U4:V4" si="1">U3-U5</f>
         <v>379.08119999999997</v>
       </c>
       <c r="V4" s="5">
@@ -1331,47 +1330,47 @@
       </c>
       <c r="AE4" s="5">
         <f>SUM(S4:V4)</f>
-        <v>1528.0411999999999</v>
+        <v>1521.6412000000003</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" ref="AF4:AN4" si="2">AF3-AF5</f>
-        <v>1556.2749072000001</v>
+        <v>1557.0725872</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="2"/>
-        <v>1602.9631544160002</v>
+        <v>1603.784764816</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="2"/>
-        <v>1635.0224175043202</v>
+        <v>1635.86046011232</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="2"/>
-        <v>1667.7228658544066</v>
+        <v>1668.5776693145665</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="2"/>
-        <v>1701.0773231714948</v>
+        <v>1701.9492227008579</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="2"/>
-        <v>1735.0988696349248</v>
+        <v>1718.9687149278666</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="2"/>
-        <v>1769.8008470276231</v>
+        <v>1736.1584020771452</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="2"/>
-        <v>1805.1968639681756</v>
+        <v>1753.5199860979167</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" si="2"/>
-        <v>1841.3008012475393</v>
+        <v>1771.0551859588959</v>
       </c>
       <c r="AO4" s="5">
         <f t="shared" ref="AO4" si="3">AO3-AO5</f>
-        <v>1878.1268172724901</v>
+        <v>1788.7657378184849</v>
       </c>
     </row>
     <row r="5" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1379,7 +1378,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:S5" si="4">C3-C4</f>
+        <f t="shared" ref="C5:T5" si="4">C3-C4</f>
         <v>126.39999999999998</v>
       </c>
       <c r="D5" s="8">
@@ -1447,11 +1446,11 @@
         <v>242.09999999999997</v>
       </c>
       <c r="T5" s="8">
-        <f t="shared" ref="T5:V5" si="5">T3*0.4</f>
-        <v>252</v>
+        <f t="shared" si="4"/>
+        <v>259.69999999999993</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="U5:V5" si="5">U3*0.4</f>
         <v>252.72080000000003</v>
       </c>
       <c r="V5" s="8">
@@ -1488,47 +1487,47 @@
       </c>
       <c r="AE5" s="8">
         <f t="shared" si="6"/>
-        <v>1008.2608000000002</v>
+        <v>1015.9607999999996</v>
       </c>
       <c r="AF5" s="8">
         <f>AF3*0.41</f>
-        <v>1081.4791728</v>
+        <v>1082.0334928</v>
       </c>
       <c r="AG5" s="8">
         <f t="shared" ref="AG5:AN5" si="7">AG3*0.41</f>
-        <v>1113.9235479839999</v>
+        <v>1114.4944975839999</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="7"/>
-        <v>1136.2020189436801</v>
+        <v>1136.78438753568</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="7"/>
-        <v>1158.9260593225538</v>
+        <v>1159.5200752863936</v>
       </c>
       <c r="AJ5" s="8">
         <f t="shared" si="7"/>
-        <v>1182.1045805090048</v>
+        <v>1182.7104767921217</v>
       </c>
       <c r="AK5" s="8">
         <f t="shared" si="7"/>
-        <v>1205.7466721191847</v>
+        <v>1194.5375815600428</v>
       </c>
       <c r="AL5" s="8">
         <f t="shared" si="7"/>
-        <v>1229.8616055615685</v>
+        <v>1206.4829573756433</v>
       </c>
       <c r="AM5" s="8">
         <f t="shared" si="7"/>
-        <v>1254.4588376728</v>
+        <v>1218.5477869493996</v>
       </c>
       <c r="AN5" s="8">
         <f t="shared" si="7"/>
-        <v>1279.548014426256</v>
+        <v>1230.7332648188935</v>
       </c>
       <c r="AO5" s="8">
         <f t="shared" ref="AO5" si="8">AO3*0.41</f>
-        <v>1305.1389747147812</v>
+        <v>1243.0405974670825</v>
       </c>
     </row>
     <row r="6" spans="2:149" x14ac:dyDescent="0.3">
@@ -1590,8 +1589,7 @@
         <v>173.1</v>
       </c>
       <c r="T6" s="5">
-        <f>P6*1.03</f>
-        <v>118.244</v>
+        <v>112.8</v>
       </c>
       <c r="U6" s="5">
         <f>Q6*1.02</f>
@@ -1625,47 +1623,47 @@
       </c>
       <c r="AE6" s="5">
         <f>SUM(S6:V6)</f>
-        <v>537.26599999999996</v>
+        <v>531.822</v>
       </c>
       <c r="AF6" s="5">
-        <f>AE6*1.02</f>
-        <v>548.01131999999996</v>
+        <f>AE6*1.01</f>
+        <v>537.14022</v>
       </c>
       <c r="AG6" s="5">
         <f>AF6*1.01</f>
-        <v>553.49143319999996</v>
+        <v>542.51162220000003</v>
       </c>
       <c r="AH6" s="5">
         <f t="shared" ref="AH6:AO6" si="9">AG6*1.01</f>
-        <v>559.02634753199993</v>
+        <v>547.93673842200008</v>
       </c>
       <c r="AI6" s="5">
         <f t="shared" si="9"/>
-        <v>564.61661100731999</v>
+        <v>553.41610580622012</v>
       </c>
       <c r="AJ6" s="5">
         <f t="shared" si="9"/>
-        <v>570.26277711739317</v>
+        <v>558.9502668642823</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="9"/>
-        <v>575.96540488856715</v>
+        <v>564.53976953292511</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="9"/>
-        <v>581.72505893745279</v>
+        <v>570.18516722825439</v>
       </c>
       <c r="AM6" s="5">
         <f t="shared" si="9"/>
-        <v>587.54230952682735</v>
+        <v>575.88701890053699</v>
       </c>
       <c r="AN6" s="5">
         <f t="shared" si="9"/>
-        <v>593.41773262209563</v>
+        <v>581.64588908954238</v>
       </c>
       <c r="AO6" s="5">
         <f t="shared" si="9"/>
-        <v>599.35190994831657</v>
+        <v>587.46234798043781</v>
       </c>
     </row>
     <row r="7" spans="2:149" x14ac:dyDescent="0.3">
@@ -1790,7 +1788,7 @@
       </c>
       <c r="T8" s="8">
         <f t="shared" si="11"/>
-        <v>133.756</v>
+        <v>146.89999999999992</v>
       </c>
       <c r="U8" s="8">
         <f t="shared" si="11"/>
@@ -1830,47 +1828,47 @@
       </c>
       <c r="AE8" s="8">
         <f t="shared" ref="AE8:AN8" si="13">AE5-AE6</f>
-        <v>470.99480000000028</v>
+        <v>484.13879999999961</v>
       </c>
       <c r="AF8" s="8">
         <f t="shared" si="13"/>
-        <v>533.46785280000006</v>
+        <v>544.89327279999998</v>
       </c>
       <c r="AG8" s="8">
         <f t="shared" si="13"/>
-        <v>560.43211478399996</v>
+        <v>571.98287538399984</v>
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="13"/>
-        <v>577.17567141168013</v>
+        <v>588.84764911367995</v>
       </c>
       <c r="AI8" s="8">
         <f t="shared" si="13"/>
-        <v>594.30944831523379</v>
+        <v>606.10396948017353</v>
       </c>
       <c r="AJ8" s="8">
         <f t="shared" si="13"/>
-        <v>611.84180339161162</v>
+        <v>623.76020992783936</v>
       </c>
       <c r="AK8" s="8">
         <f t="shared" si="13"/>
-        <v>629.78126723061757</v>
+        <v>629.99781202711767</v>
       </c>
       <c r="AL8" s="8">
         <f t="shared" si="13"/>
-        <v>648.13654662411568</v>
+        <v>636.29779014738892</v>
       </c>
       <c r="AM8" s="8">
         <f t="shared" si="13"/>
-        <v>666.91652814597262</v>
+        <v>642.66076804886256</v>
       </c>
       <c r="AN8" s="8">
         <f t="shared" si="13"/>
-        <v>686.1302818041604</v>
+        <v>649.08737572935115</v>
       </c>
       <c r="AO8" s="8">
         <f t="shared" ref="AO8" si="14">AO5-AO6</f>
-        <v>705.7870647664646</v>
+        <v>655.57824948664472</v>
       </c>
     </row>
     <row r="9" spans="2:149" x14ac:dyDescent="0.3">
@@ -1932,7 +1930,7 @@
         <v>3.1</v>
       </c>
       <c r="T9" s="5">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U9" s="5">
         <v>3</v>
@@ -1964,47 +1962,47 @@
       </c>
       <c r="AE9" s="5">
         <f t="shared" ref="AE9:AE10" si="17">SUM(S9:V9)</f>
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="AF9" s="5">
         <f t="shared" ref="AF9:AO9" si="18">AE9*1.03</f>
-        <v>12.462999999999999</v>
+        <v>12.257000000000001</v>
       </c>
       <c r="AG9" s="5">
         <f t="shared" si="18"/>
-        <v>12.83689</v>
+        <v>12.624710000000002</v>
       </c>
       <c r="AH9" s="5">
         <f t="shared" si="18"/>
-        <v>13.2219967</v>
+        <v>13.003451300000002</v>
       </c>
       <c r="AI9" s="5">
         <f t="shared" si="18"/>
-        <v>13.618656601</v>
+        <v>13.393554839000002</v>
       </c>
       <c r="AJ9" s="5">
         <f t="shared" si="18"/>
-        <v>14.02721629903</v>
+        <v>13.795361484170002</v>
       </c>
       <c r="AK9" s="5">
         <f t="shared" si="18"/>
-        <v>14.4480327880009</v>
+        <v>14.209222328695102</v>
       </c>
       <c r="AL9" s="5">
         <f t="shared" si="18"/>
-        <v>14.881473771640927</v>
+        <v>14.635498998555954</v>
       </c>
       <c r="AM9" s="5">
         <f t="shared" si="18"/>
-        <v>15.327917984790155</v>
+        <v>15.074563968512633</v>
       </c>
       <c r="AN9" s="5">
         <f t="shared" si="18"/>
-        <v>15.787755524333859</v>
+        <v>15.526800887568012</v>
       </c>
       <c r="AO9" s="5">
         <f t="shared" si="18"/>
-        <v>16.261388190063876</v>
+        <v>15.992604914195052</v>
       </c>
     </row>
     <row r="10" spans="2:149" x14ac:dyDescent="0.3">
@@ -2066,7 +2064,7 @@
         <v>-16.899999999999999</v>
       </c>
       <c r="T10" s="5">
-        <v>-10</v>
+        <v>10.8</v>
       </c>
       <c r="U10" s="5">
         <v>-10</v>
@@ -2098,47 +2096,47 @@
       </c>
       <c r="AE10" s="5">
         <f t="shared" si="17"/>
-        <v>-46.9</v>
+        <v>-26.099999999999998</v>
       </c>
       <c r="AF10" s="5">
         <f t="shared" ref="AF10:AO10" si="19">AE10*1.03</f>
-        <v>-48.307000000000002</v>
+        <v>-26.882999999999999</v>
       </c>
       <c r="AG10" s="5">
         <f t="shared" si="19"/>
-        <v>-49.756210000000003</v>
+        <v>-27.689489999999999</v>
       </c>
       <c r="AH10" s="5">
         <f t="shared" si="19"/>
-        <v>-51.248896300000006</v>
+        <v>-28.520174699999998</v>
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="19"/>
-        <v>-52.786363189000006</v>
+        <v>-29.375779940999998</v>
       </c>
       <c r="AJ10" s="5">
         <f t="shared" si="19"/>
-        <v>-54.369954084670006</v>
+        <v>-30.257053339229998</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="19"/>
-        <v>-56.001052707210107</v>
+        <v>-31.164764939406897</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="19"/>
-        <v>-57.681084288426412</v>
+        <v>-32.099707887589105</v>
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="19"/>
-        <v>-59.411516817079203</v>
+        <v>-33.062699124216778</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="19"/>
-        <v>-61.193862321591581</v>
+        <v>-34.05458009794328</v>
       </c>
       <c r="AO10" s="5">
         <f t="shared" si="19"/>
-        <v>-63.029678191239327</v>
+        <v>-35.076217500881576</v>
       </c>
     </row>
     <row r="11" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2215,7 +2213,7 @@
       </c>
       <c r="T11" s="8">
         <f t="shared" ref="T11" si="22">T8-T9-T10</f>
-        <v>140.756</v>
+        <v>133.2999999999999</v>
       </c>
       <c r="U11" s="8">
         <f t="shared" ref="U11" si="23">U8-U9-U10</f>
@@ -2255,47 +2253,47 @@
       </c>
       <c r="AE11" s="8">
         <f t="shared" si="25"/>
-        <v>505.79480000000024</v>
+        <v>498.33879999999965</v>
       </c>
       <c r="AF11" s="8">
         <f t="shared" ref="AF11:AN11" si="26">AF8-AF9-AF10</f>
-        <v>569.31185280000011</v>
+        <v>559.51927280000007</v>
       </c>
       <c r="AG11" s="8">
         <f t="shared" si="26"/>
-        <v>597.35143478399993</v>
+        <v>587.04765538399977</v>
       </c>
       <c r="AH11" s="8">
         <f t="shared" si="26"/>
-        <v>615.20257101168011</v>
+        <v>604.36437251367988</v>
       </c>
       <c r="AI11" s="8">
         <f t="shared" si="26"/>
-        <v>633.47715490323378</v>
+        <v>622.08619458217356</v>
       </c>
       <c r="AJ11" s="8">
         <f t="shared" si="26"/>
-        <v>652.18454117725162</v>
+        <v>640.22190178289929</v>
       </c>
       <c r="AK11" s="8">
         <f t="shared" si="26"/>
-        <v>671.33428714982676</v>
+        <v>646.95335463782953</v>
       </c>
       <c r="AL11" s="8">
         <f t="shared" si="26"/>
-        <v>690.93615714090117</v>
+        <v>653.76199903642214</v>
       </c>
       <c r="AM11" s="8">
         <f t="shared" si="26"/>
-        <v>711.00012697826173</v>
+        <v>660.64890320456675</v>
       </c>
       <c r="AN11" s="8">
         <f t="shared" si="26"/>
-        <v>731.53638860141814</v>
+        <v>667.61515493972638</v>
       </c>
       <c r="AO11" s="8">
         <f t="shared" ref="AO11" si="27">AO8-AO9-AO10</f>
-        <v>752.5553547676401</v>
+        <v>674.66186207333135</v>
       </c>
     </row>
     <row r="12" spans="2:149" x14ac:dyDescent="0.3">
@@ -2357,11 +2355,10 @@
         <v>14.4</v>
       </c>
       <c r="T12" s="5">
-        <f t="shared" ref="T12:V12" si="30">T11*0.24</f>
-        <v>33.781439999999996</v>
+        <v>34</v>
       </c>
       <c r="U12" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="U12:V12" si="30">U11*0.24</f>
         <v>33.324192000000004</v>
       </c>
       <c r="V12" s="5">
@@ -2392,47 +2389,47 @@
       </c>
       <c r="AE12" s="5">
         <f t="shared" ref="AE12:AE13" si="31">SUM(S12:V12)</f>
-        <v>115.91875199999998</v>
+        <v>116.13731200000001</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" ref="AF12:AN12" si="32">AF11*0.25</f>
-        <v>142.32796320000003</v>
+        <v>139.87981820000002</v>
       </c>
       <c r="AG12" s="5">
         <f t="shared" si="32"/>
-        <v>149.33785869599998</v>
+        <v>146.76191384599994</v>
       </c>
       <c r="AH12" s="5">
         <f t="shared" si="32"/>
-        <v>153.80064275292003</v>
+        <v>151.09109312841997</v>
       </c>
       <c r="AI12" s="5">
         <f t="shared" si="32"/>
-        <v>158.36928872580845</v>
+        <v>155.52154864554339</v>
       </c>
       <c r="AJ12" s="5">
         <f t="shared" si="32"/>
-        <v>163.0461352943129</v>
+        <v>160.05547544572482</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="32"/>
-        <v>167.83357178745669</v>
+        <v>161.73833865945738</v>
       </c>
       <c r="AL12" s="5">
         <f t="shared" si="32"/>
-        <v>172.73403928522529</v>
+        <v>163.44049975910553</v>
       </c>
       <c r="AM12" s="5">
         <f t="shared" si="32"/>
-        <v>177.75003174456543</v>
+        <v>165.16222580114169</v>
       </c>
       <c r="AN12" s="5">
         <f t="shared" si="32"/>
-        <v>182.88409715035453</v>
+        <v>166.9037887349316</v>
       </c>
       <c r="AO12" s="5">
         <f t="shared" ref="AO12" si="33">AO11*0.25</f>
-        <v>188.13883869191002</v>
+        <v>168.66546551833284</v>
       </c>
     </row>
     <row r="13" spans="2:149" x14ac:dyDescent="0.3">
@@ -2494,7 +2491,7 @@
         <v>-0.4</v>
       </c>
       <c r="T13" s="5">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="U13" s="5">
         <v>0</v>
@@ -2526,47 +2523,47 @@
       </c>
       <c r="AE13" s="5">
         <f t="shared" si="31"/>
-        <v>-0.4</v>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" ref="AF13:AN13" si="34">AF11*0.01</f>
-        <v>5.6931185280000012</v>
+        <v>5.5951927280000007</v>
       </c>
       <c r="AG13" s="5">
         <f t="shared" si="34"/>
-        <v>5.9735143478399992</v>
+        <v>5.8704765538399979</v>
       </c>
       <c r="AH13" s="5">
         <f t="shared" si="34"/>
-        <v>6.152025710116801</v>
+        <v>6.0436437251367989</v>
       </c>
       <c r="AI13" s="5">
         <f t="shared" si="34"/>
-        <v>6.3347715490323377</v>
+        <v>6.2208619458217358</v>
       </c>
       <c r="AJ13" s="5">
         <f t="shared" si="34"/>
-        <v>6.5218454117725164</v>
+        <v>6.4022190178289931</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="34"/>
-        <v>6.7133428714982681</v>
+        <v>6.4695335463782957</v>
       </c>
       <c r="AL13" s="5">
         <f t="shared" si="34"/>
-        <v>6.9093615714090122</v>
+        <v>6.5376199903642211</v>
       </c>
       <c r="AM13" s="5">
         <f t="shared" si="34"/>
-        <v>7.1100012697826172</v>
+        <v>6.6064890320456673</v>
       </c>
       <c r="AN13" s="5">
         <f t="shared" si="34"/>
-        <v>7.3153638860141816</v>
+        <v>6.6761515493972636</v>
       </c>
       <c r="AO13" s="5">
         <f t="shared" ref="AO13" si="35">AO11*0.01</f>
-        <v>7.5255535476764015</v>
+        <v>6.7466186207333134</v>
       </c>
     </row>
     <row r="14" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2643,7 +2640,7 @@
       </c>
       <c r="T14" s="8">
         <f t="shared" ref="T14" si="37">T11-T12-T13</f>
-        <v>106.97456</v>
+        <v>99.499999999999901</v>
       </c>
       <c r="U14" s="8">
         <f t="shared" ref="U14" si="38">U11-U12-U13</f>
@@ -2683,479 +2680,479 @@
       </c>
       <c r="AE14" s="8">
         <f t="shared" si="40"/>
-        <v>390.27604800000023</v>
+        <v>382.80148799999967</v>
       </c>
       <c r="AF14" s="8">
         <f t="shared" ref="AF14:AN14" si="41">AF11-AF12-AF13</f>
-        <v>421.2907710720001</v>
+        <v>414.04426187199999</v>
       </c>
       <c r="AG14" s="8">
         <f t="shared" si="41"/>
-        <v>442.0400617401599</v>
+        <v>434.41526498415982</v>
       </c>
       <c r="AH14" s="8">
         <f t="shared" si="41"/>
-        <v>455.24990254864332</v>
+        <v>447.22963566012311</v>
       </c>
       <c r="AI14" s="8">
         <f t="shared" si="41"/>
-        <v>468.77309462839298</v>
+        <v>460.34378399080845</v>
       </c>
       <c r="AJ14" s="8">
         <f t="shared" si="41"/>
-        <v>482.61656047116622</v>
+        <v>473.76420731934547</v>
       </c>
       <c r="AK14" s="8">
         <f t="shared" si="41"/>
-        <v>496.78737249087186</v>
+        <v>478.74548243199388</v>
       </c>
       <c r="AL14" s="8">
         <f t="shared" si="41"/>
-        <v>511.29275628426683</v>
+        <v>483.78387928695236</v>
       </c>
       <c r="AM14" s="8">
         <f t="shared" si="41"/>
-        <v>526.14009396391373</v>
+        <v>488.8801883713794</v>
       </c>
       <c r="AN14" s="8">
         <f t="shared" si="41"/>
-        <v>541.33692756504934</v>
+        <v>494.03521465539751</v>
       </c>
       <c r="AO14" s="8">
         <f t="shared" ref="AO14" si="42">AO11-AO12-AO13</f>
-        <v>556.89096252805371</v>
+        <v>499.24977793426518</v>
       </c>
       <c r="AP14" s="1">
         <f>AO14*(1+$AR$19)</f>
-        <v>551.32205290277318</v>
+        <v>494.25728015492251</v>
       </c>
       <c r="AQ14" s="1">
         <f t="shared" ref="AQ14:DB14" si="43">AP14*(1+$AR$19)</f>
-        <v>545.80883237374542</v>
+        <v>489.31470735337331</v>
       </c>
       <c r="AR14" s="1">
         <f t="shared" si="43"/>
-        <v>540.35074405000796</v>
+        <v>484.42156027983958</v>
       </c>
       <c r="AS14" s="1">
         <f t="shared" si="43"/>
-        <v>534.94723660950785</v>
+        <v>479.5773446770412</v>
       </c>
       <c r="AT14" s="1">
         <f t="shared" si="43"/>
-        <v>529.59776424341283</v>
+        <v>474.7815712302708</v>
       </c>
       <c r="AU14" s="1">
         <f t="shared" si="43"/>
-        <v>524.30178660097874</v>
+        <v>470.03375551796807</v>
       </c>
       <c r="AV14" s="1">
         <f t="shared" si="43"/>
-        <v>519.05876873496891</v>
+        <v>465.33341796278842</v>
       </c>
       <c r="AW14" s="1">
         <f t="shared" si="43"/>
-        <v>513.86818104761926</v>
+        <v>460.68008378316051</v>
       </c>
       <c r="AX14" s="1">
         <f t="shared" si="43"/>
-        <v>508.72949923714305</v>
+        <v>456.07328294532891</v>
       </c>
       <c r="AY14" s="1">
         <f t="shared" si="43"/>
-        <v>503.64220424477162</v>
+        <v>451.51255011587563</v>
       </c>
       <c r="AZ14" s="1">
         <f t="shared" si="43"/>
-        <v>498.60578220232389</v>
+        <v>446.99742461471686</v>
       </c>
       <c r="BA14" s="1">
         <f t="shared" si="43"/>
-        <v>493.61972438030062</v>
+        <v>442.5274503685697</v>
       </c>
       <c r="BB14" s="1">
         <f t="shared" si="43"/>
-        <v>488.68352713649762</v>
+        <v>438.10217586488398</v>
       </c>
       <c r="BC14" s="1">
         <f t="shared" si="43"/>
-        <v>483.79669186513263</v>
+        <v>433.72115410623513</v>
       </c>
       <c r="BD14" s="1">
         <f t="shared" si="43"/>
-        <v>478.95872494648131</v>
+        <v>429.38394256517279</v>
       </c>
       <c r="BE14" s="1">
         <f t="shared" si="43"/>
-        <v>474.16913769701648</v>
+        <v>425.09010313952103</v>
       </c>
       <c r="BF14" s="1">
         <f t="shared" si="43"/>
-        <v>469.42744632004633</v>
+        <v>420.83920210812585</v>
       </c>
       <c r="BG14" s="1">
         <f t="shared" si="43"/>
-        <v>464.73317185684584</v>
+        <v>416.63081008704461</v>
       </c>
       <c r="BH14" s="1">
         <f t="shared" si="43"/>
-        <v>460.08584013827738</v>
+        <v>412.46450198617418</v>
       </c>
       <c r="BI14" s="1">
         <f t="shared" si="43"/>
-        <v>455.48498173689461</v>
+        <v>408.33985696631242</v>
       </c>
       <c r="BJ14" s="1">
         <f t="shared" si="43"/>
-        <v>450.93013191952565</v>
+        <v>404.25645839664929</v>
       </c>
       <c r="BK14" s="1">
         <f t="shared" si="43"/>
-        <v>446.42083060033036</v>
+        <v>400.21389381268278</v>
       </c>
       <c r="BL14" s="1">
         <f t="shared" si="43"/>
-        <v>441.95662229432708</v>
+        <v>396.21175487455594</v>
       </c>
       <c r="BM14" s="1">
         <f t="shared" si="43"/>
-        <v>437.5370560713838</v>
+        <v>392.2496373258104</v>
       </c>
       <c r="BN14" s="1">
         <f t="shared" si="43"/>
-        <v>433.16168551066994</v>
+        <v>388.32714095255227</v>
       </c>
       <c r="BO14" s="1">
         <f t="shared" si="43"/>
-        <v>428.83006865556325</v>
+        <v>384.44386954302672</v>
       </c>
       <c r="BP14" s="1">
         <f t="shared" si="43"/>
-        <v>424.54176796900759</v>
+        <v>380.59943084759647</v>
       </c>
       <c r="BQ14" s="1">
         <f t="shared" si="43"/>
-        <v>420.2963502893175</v>
+        <v>376.79343653912048</v>
       </c>
       <c r="BR14" s="1">
         <f t="shared" si="43"/>
-        <v>416.09338678642433</v>
+        <v>373.02550217372925</v>
       </c>
       <c r="BS14" s="1">
         <f t="shared" si="43"/>
-        <v>411.9324529185601</v>
+        <v>369.29524715199193</v>
       </c>
       <c r="BT14" s="1">
         <f t="shared" si="43"/>
-        <v>407.81312838937447</v>
+        <v>365.60229468047203</v>
       </c>
       <c r="BU14" s="1">
         <f t="shared" si="43"/>
-        <v>403.73499710548072</v>
+        <v>361.94627173366729</v>
       </c>
       <c r="BV14" s="1">
         <f t="shared" si="43"/>
-        <v>399.69764713442589</v>
+        <v>358.32680901633063</v>
       </c>
       <c r="BW14" s="1">
         <f t="shared" si="43"/>
-        <v>395.70067066308161</v>
+        <v>354.74354092616733</v>
       </c>
       <c r="BX14" s="1">
         <f t="shared" si="43"/>
-        <v>391.7436639564508</v>
+        <v>351.19610551690567</v>
       </c>
       <c r="BY14" s="1">
         <f t="shared" si="43"/>
-        <v>387.82622731688627</v>
+        <v>347.68414446173659</v>
       </c>
       <c r="BZ14" s="1">
         <f t="shared" si="43"/>
-        <v>383.94796504371743</v>
+        <v>344.20730301711922</v>
       </c>
       <c r="CA14" s="1">
         <f t="shared" si="43"/>
-        <v>380.10848539328026</v>
+        <v>340.76522998694804</v>
       </c>
       <c r="CB14" s="1">
         <f t="shared" si="43"/>
-        <v>376.30740053934744</v>
+        <v>337.35757768707856</v>
       </c>
       <c r="CC14" s="1">
         <f t="shared" si="43"/>
-        <v>372.54432653395395</v>
+        <v>333.98400191020778</v>
       </c>
       <c r="CD14" s="1">
         <f t="shared" si="43"/>
-        <v>368.8188832686144</v>
+        <v>330.64416189110568</v>
       </c>
       <c r="CE14" s="1">
         <f t="shared" si="43"/>
-        <v>365.13069443592826</v>
+        <v>327.33772027219464</v>
       </c>
       <c r="CF14" s="1">
         <f t="shared" si="43"/>
-        <v>361.47938749156896</v>
+        <v>324.06434306947267</v>
       </c>
       <c r="CG14" s="1">
         <f t="shared" si="43"/>
-        <v>357.86459361665328</v>
+        <v>320.82369963877795</v>
       </c>
       <c r="CH14" s="1">
         <f t="shared" si="43"/>
-        <v>354.28594768048674</v>
+        <v>317.61546264239018</v>
       </c>
       <c r="CI14" s="1">
         <f t="shared" si="43"/>
-        <v>350.74308820368185</v>
+        <v>314.43930801596628</v>
       </c>
       <c r="CJ14" s="1">
         <f t="shared" si="43"/>
-        <v>347.23565732164502</v>
+        <v>311.29491493580662</v>
       </c>
       <c r="CK14" s="1">
         <f t="shared" si="43"/>
-        <v>343.76330074842855</v>
+        <v>308.18196578644853</v>
       </c>
       <c r="CL14" s="1">
         <f t="shared" si="43"/>
-        <v>340.32566774094425</v>
+        <v>305.10014612858402</v>
       </c>
       <c r="CM14" s="1">
         <f t="shared" si="43"/>
-        <v>336.92241106353481</v>
+        <v>302.04914466729815</v>
       </c>
       <c r="CN14" s="1">
         <f t="shared" si="43"/>
-        <v>333.55318695289947</v>
+        <v>299.02865322062519</v>
       </c>
       <c r="CO14" s="1">
         <f t="shared" si="43"/>
-        <v>330.21765508337046</v>
+        <v>296.03836668841893</v>
       </c>
       <c r="CP14" s="1">
         <f t="shared" si="43"/>
-        <v>326.91547853253672</v>
+        <v>293.07798302153475</v>
       </c>
       <c r="CQ14" s="1">
         <f t="shared" si="43"/>
-        <v>323.64632374721134</v>
+        <v>290.14720319131942</v>
       </c>
       <c r="CR14" s="1">
         <f t="shared" si="43"/>
-        <v>320.40986050973925</v>
+        <v>287.2457311594062</v>
       </c>
       <c r="CS14" s="1">
         <f t="shared" si="43"/>
-        <v>317.20576190464186</v>
+        <v>284.37327384781213</v>
       </c>
       <c r="CT14" s="1">
         <f t="shared" si="43"/>
-        <v>314.03370428559543</v>
+        <v>281.52954110933399</v>
       </c>
       <c r="CU14" s="1">
         <f t="shared" si="43"/>
-        <v>310.89336724273949</v>
+        <v>278.71424569824063</v>
       </c>
       <c r="CV14" s="1">
         <f t="shared" si="43"/>
-        <v>307.7844335703121</v>
+        <v>275.92710324125824</v>
       </c>
       <c r="CW14" s="1">
         <f t="shared" si="43"/>
-        <v>304.706589234609</v>
+        <v>273.16783220884565</v>
       </c>
       <c r="CX14" s="1">
         <f t="shared" si="43"/>
-        <v>301.6595233422629</v>
+        <v>270.43615388675721</v>
       </c>
       <c r="CY14" s="1">
         <f t="shared" si="43"/>
-        <v>298.64292810884029</v>
+        <v>267.73179234788961</v>
       </c>
       <c r="CZ14" s="1">
         <f t="shared" si="43"/>
-        <v>295.65649882775188</v>
+        <v>265.05447442441073</v>
       </c>
       <c r="DA14" s="1">
         <f t="shared" si="43"/>
-        <v>292.69993383947434</v>
+        <v>262.40392968016664</v>
       </c>
       <c r="DB14" s="1">
         <f t="shared" si="43"/>
-        <v>289.77293450107959</v>
+        <v>259.779890383365</v>
       </c>
       <c r="DC14" s="1">
         <f t="shared" ref="DC14:ES14" si="44">DB14*(1+$AR$19)</f>
-        <v>286.87520515606877</v>
+        <v>257.18209147953132</v>
       </c>
       <c r="DD14" s="1">
         <f t="shared" si="44"/>
-        <v>284.00645310450807</v>
+        <v>254.610270564736</v>
       </c>
       <c r="DE14" s="1">
         <f t="shared" si="44"/>
-        <v>281.166388573463</v>
+        <v>252.06416785908863</v>
       </c>
       <c r="DF14" s="1">
         <f t="shared" si="44"/>
-        <v>278.35472468772838</v>
+        <v>249.54352618049774</v>
       </c>
       <c r="DG14" s="1">
         <f t="shared" si="44"/>
-        <v>275.5711774408511</v>
+        <v>247.04809091869276</v>
       </c>
       <c r="DH14" s="1">
         <f t="shared" si="44"/>
-        <v>272.81546566644261</v>
+        <v>244.57761000950583</v>
       </c>
       <c r="DI14" s="1">
         <f t="shared" si="44"/>
-        <v>270.0873110097782</v>
+        <v>242.13183390941077</v>
       </c>
       <c r="DJ14" s="1">
         <f t="shared" si="44"/>
-        <v>267.3864378996804</v>
+        <v>239.71051557031666</v>
       </c>
       <c r="DK14" s="1">
         <f t="shared" si="44"/>
-        <v>264.71257352068358</v>
+        <v>237.31341041461349</v>
       </c>
       <c r="DL14" s="1">
         <f t="shared" si="44"/>
-        <v>262.06544778547675</v>
+        <v>234.94027631046734</v>
       </c>
       <c r="DM14" s="1">
         <f t="shared" si="44"/>
-        <v>259.44479330762198</v>
+        <v>232.59087354736266</v>
       </c>
       <c r="DN14" s="1">
         <f t="shared" si="44"/>
-        <v>256.85034537454578</v>
+        <v>230.26496481188903</v>
       </c>
       <c r="DO14" s="1">
         <f t="shared" si="44"/>
-        <v>254.28184192080033</v>
+        <v>227.96231516377014</v>
       </c>
       <c r="DP14" s="1">
         <f t="shared" si="44"/>
-        <v>251.73902350159233</v>
+        <v>225.68269201213243</v>
       </c>
       <c r="DQ14" s="1">
         <f t="shared" si="44"/>
-        <v>249.22163326657639</v>
+        <v>223.42586509201112</v>
       </c>
       <c r="DR14" s="1">
         <f t="shared" si="44"/>
-        <v>246.72941693391061</v>
+        <v>221.19160644109101</v>
       </c>
       <c r="DS14" s="1">
         <f t="shared" si="44"/>
-        <v>244.2621227645715</v>
+        <v>218.97969037668011</v>
       </c>
       <c r="DT14" s="1">
         <f t="shared" si="44"/>
-        <v>241.81950153692577</v>
+        <v>216.78989347291332</v>
       </c>
       <c r="DU14" s="1">
         <f t="shared" si="44"/>
-        <v>239.40130652155651</v>
+        <v>214.6219945381842</v>
       </c>
       <c r="DV14" s="1">
         <f t="shared" si="44"/>
-        <v>237.00729345634093</v>
+        <v>212.47577459280237</v>
       </c>
       <c r="DW14" s="1">
         <f t="shared" si="44"/>
-        <v>234.63722052177752</v>
+        <v>210.35101684687433</v>
       </c>
       <c r="DX14" s="1">
         <f t="shared" si="44"/>
-        <v>232.29084831655973</v>
+        <v>208.24750667840559</v>
       </c>
       <c r="DY14" s="1">
         <f t="shared" si="44"/>
-        <v>229.96793983339413</v>
+        <v>206.16503161162152</v>
       </c>
       <c r="DZ14" s="1">
         <f t="shared" si="44"/>
-        <v>227.66826043506018</v>
+        <v>204.1033812955053</v>
       </c>
       <c r="EA14" s="1">
         <f t="shared" si="44"/>
-        <v>225.39157783070956</v>
+        <v>202.06234748255025</v>
       </c>
       <c r="EB14" s="1">
         <f t="shared" si="44"/>
-        <v>223.13766205240248</v>
+        <v>200.04172400772475</v>
       </c>
       <c r="EC14" s="1">
         <f t="shared" si="44"/>
-        <v>220.90628543187844</v>
+        <v>198.04130676764751</v>
       </c>
       <c r="ED14" s="1">
         <f t="shared" si="44"/>
-        <v>218.69722257755967</v>
+        <v>196.06089369997105</v>
       </c>
       <c r="EE14" s="1">
         <f t="shared" si="44"/>
-        <v>216.51025035178407</v>
+        <v>194.10028476297134</v>
       </c>
       <c r="EF14" s="1">
         <f t="shared" si="44"/>
-        <v>214.34514784826624</v>
+        <v>192.15928191534164</v>
       </c>
       <c r="EG14" s="1">
         <f t="shared" si="44"/>
-        <v>212.20169636978358</v>
+        <v>190.23768909618821</v>
       </c>
       <c r="EH14" s="1">
         <f t="shared" si="44"/>
-        <v>210.07967940608575</v>
+        <v>188.33531220522633</v>
       </c>
       <c r="EI14" s="1">
         <f t="shared" si="44"/>
-        <v>207.97888261202488</v>
+        <v>186.45195908317407</v>
       </c>
       <c r="EJ14" s="1">
         <f t="shared" si="44"/>
-        <v>205.89909378590463</v>
+        <v>184.58743949234233</v>
       </c>
       <c r="EK14" s="1">
         <f t="shared" si="44"/>
-        <v>203.84010284804558</v>
+        <v>182.74156509741891</v>
       </c>
       <c r="EL14" s="1">
         <f t="shared" si="44"/>
-        <v>201.80170181956512</v>
+        <v>180.91414944644472</v>
       </c>
       <c r="EM14" s="1">
         <f t="shared" si="44"/>
-        <v>199.78368480136947</v>
+        <v>179.10500795198027</v>
       </c>
       <c r="EN14" s="1">
         <f t="shared" si="44"/>
-        <v>197.78584795335578</v>
+        <v>177.31395787246046</v>
       </c>
       <c r="EO14" s="1">
         <f t="shared" si="44"/>
-        <v>195.80798947382223</v>
+        <v>175.54081829373587</v>
       </c>
       <c r="EP14" s="1">
         <f t="shared" si="44"/>
-        <v>193.849909579084</v>
+        <v>173.78541011079849</v>
       </c>
       <c r="EQ14" s="1">
         <f t="shared" si="44"/>
-        <v>191.91141048329317</v>
+        <v>172.04755600969051</v>
       </c>
       <c r="ER14" s="1">
         <f t="shared" si="44"/>
-        <v>189.99229637846022</v>
+        <v>170.32708044959361</v>
       </c>
       <c r="ES14" s="1">
         <f t="shared" si="44"/>
-        <v>188.09237341467562</v>
+        <v>168.62380964509768</v>
       </c>
     </row>
     <row r="15" spans="2:149" x14ac:dyDescent="0.3">
@@ -3368,7 +3365,7 @@
       </c>
       <c r="T16" s="7">
         <f t="shared" ref="T16" si="48">T14/T15</f>
-        <v>2.4648516129032259</v>
+        <v>2.292626728110597</v>
       </c>
       <c r="U16" s="7">
         <f t="shared" ref="U16" si="49">U14/U15</f>
@@ -3408,47 +3405,47 @@
       </c>
       <c r="AE16" s="7">
         <f t="shared" si="51"/>
-        <v>8.9925356682027697</v>
+        <v>8.8203107834101306</v>
       </c>
       <c r="AF16" s="7">
         <f t="shared" ref="AF16:AN16" si="52">AF14/AF15</f>
-        <v>9.7071606237788046</v>
+        <v>9.5401903657142864</v>
       </c>
       <c r="AG16" s="7">
         <f t="shared" si="52"/>
-        <v>10.185254878805528</v>
+        <v>10.00956831760737</v>
       </c>
       <c r="AH16" s="7">
         <f t="shared" si="52"/>
-        <v>10.489629090982564</v>
+        <v>10.304830314749381</v>
       </c>
       <c r="AI16" s="7">
         <f t="shared" si="52"/>
-        <v>10.801223378534401</v>
+        <v>10.606999631124619</v>
       </c>
       <c r="AJ16" s="7">
         <f t="shared" si="52"/>
-        <v>11.120197245879407</v>
+        <v>10.916225975100126</v>
       </c>
       <c r="AK16" s="7">
         <f t="shared" si="52"/>
-        <v>11.446713651863407</v>
+        <v>11.031001899354697</v>
       </c>
       <c r="AL16" s="7">
         <f t="shared" si="52"/>
-        <v>11.780939084890941</v>
+        <v>11.147093992786921</v>
       </c>
       <c r="AM16" s="7">
         <f t="shared" si="52"/>
-        <v>12.123043639721514</v>
+        <v>11.264520469386623</v>
       </c>
       <c r="AN16" s="7">
         <f t="shared" si="52"/>
-        <v>12.473201095968879</v>
+        <v>11.383299876852478</v>
       </c>
       <c r="AO16" s="7">
         <f t="shared" ref="AO16" si="53">AO14/AO15</f>
-        <v>12.831588998342252</v>
+        <v>11.503451104476156</v>
       </c>
     </row>
     <row r="18" spans="2:44" x14ac:dyDescent="0.3">
@@ -3513,7 +3510,7 @@
       </c>
       <c r="T18" s="10">
         <f t="shared" si="55"/>
-        <v>7.2888283378746532E-2</v>
+        <v>7.5102179836512128E-2</v>
       </c>
       <c r="U18" s="10">
         <f t="shared" si="55"/>
@@ -3550,7 +3547,7 @@
       </c>
       <c r="AE18" s="10">
         <f t="shared" si="56"/>
-        <v>5.4463892237974543E-2</v>
+        <v>5.5004365359830221E-2</v>
       </c>
       <c r="AF18" s="10">
         <f t="shared" si="56"/>
@@ -3574,23 +3571,23 @@
       </c>
       <c r="AK18" s="10">
         <f t="shared" si="56"/>
-        <v>2.0000000000000018E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL18" s="10">
         <f t="shared" si="56"/>
-        <v>2.0000000000000018E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM18" s="10">
         <f t="shared" si="56"/>
-        <v>2.0000000000000018E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN18" s="10">
         <f t="shared" si="56"/>
-        <v>2.0000000000000018E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO18" s="10">
         <f t="shared" si="56"/>
-        <v>2.0000000000000018E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
     </row>
     <row r="19" spans="2:44" x14ac:dyDescent="0.3">
@@ -3667,7 +3664,7 @@
       </c>
       <c r="T19" s="10">
         <f t="shared" si="58"/>
-        <v>0.4</v>
+        <v>0.41137335656581647</v>
       </c>
       <c r="U19" s="10">
         <f t="shared" si="58"/>
@@ -3707,7 +3704,7 @@
       </c>
       <c r="AE19" s="10">
         <f t="shared" si="59"/>
-        <v>0.39753183966262701</v>
+        <v>0.40036254700303658</v>
       </c>
       <c r="AF19" s="10">
         <f t="shared" si="59"/>
@@ -3719,23 +3716,23 @@
       </c>
       <c r="AH19" s="10">
         <f t="shared" si="59"/>
-        <v>0.41</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="AI19" s="10">
         <f t="shared" si="59"/>
-        <v>0.41000000000000003</v>
+        <v>0.41</v>
       </c>
       <c r="AJ19" s="10">
         <f t="shared" si="59"/>
-        <v>0.41</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="AK19" s="10">
         <f t="shared" si="59"/>
-        <v>0.40999999999999992</v>
+        <v>0.41</v>
       </c>
       <c r="AL19" s="10">
         <f t="shared" si="59"/>
-        <v>0.41</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="AM19" s="10">
         <f t="shared" si="59"/>
@@ -3818,7 +3815,7 @@
       </c>
       <c r="T20" s="10">
         <f t="shared" si="62"/>
-        <v>3.0000000000000027E-2</v>
+        <v>-1.7421602787456414E-2</v>
       </c>
       <c r="U20" s="10">
         <f t="shared" si="62"/>
@@ -3855,11 +3852,11 @@
       </c>
       <c r="AE20" s="10">
         <f t="shared" si="63"/>
-        <v>2.4534706331045042E-2</v>
+        <v>1.415331807780329E-2</v>
       </c>
       <c r="AF20" s="10">
         <f t="shared" si="63"/>
-        <v>2.0000000000000018E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG20" s="10">
         <f t="shared" si="63"/>
@@ -3978,7 +3975,7 @@
       </c>
       <c r="T21" s="10">
         <f t="shared" si="65"/>
-        <v>0.21231111111111112</v>
+        <v>0.2326944400443528</v>
       </c>
       <c r="U21" s="10">
         <f t="shared" si="65"/>
@@ -4018,54 +4015,54 @@
       </c>
       <c r="AE21" s="10">
         <f t="shared" si="66"/>
-        <v>0.18570138729536162</v>
+        <v>0.19078594673238736</v>
       </c>
       <c r="AF21" s="10">
         <f t="shared" si="66"/>
-        <v>0.20224321017825894</v>
+        <v>0.20646887858331181</v>
       </c>
       <c r="AG21" s="10">
         <f t="shared" si="66"/>
-        <v>0.20627732260198203</v>
+        <v>0.21042093919334454</v>
       </c>
       <c r="AH21" s="10">
         <f t="shared" si="66"/>
-        <v>0.20827460375294304</v>
+        <v>0.21237759665223335</v>
       </c>
       <c r="AI21" s="10">
         <f t="shared" si="66"/>
-        <v>0.2102523037161495</v>
+        <v>0.21431507119485851</v>
       </c>
       <c r="AJ21" s="10">
         <f t="shared" si="66"/>
-        <v>0.21221061446403036</v>
+        <v>0.2162335508890266</v>
       </c>
       <c r="AK21" s="10">
         <f t="shared" si="66"/>
-        <v>0.21414972608693195</v>
+        <v>0.21623355088902657</v>
       </c>
       <c r="AL21" s="10">
         <f t="shared" si="66"/>
-        <v>0.21606982681156991</v>
+        <v>0.2162335508890266</v>
       </c>
       <c r="AM21" s="10">
         <f t="shared" si="66"/>
-        <v>0.21797110301929964</v>
+        <v>0.21623355088902652</v>
       </c>
       <c r="AN21" s="10">
         <f t="shared" si="66"/>
-        <v>0.21985373926420848</v>
+        <v>0.21623355088902649</v>
       </c>
       <c r="AO21" s="10">
         <f t="shared" ref="AO21" si="67">AO8/AO3</f>
-        <v>0.22171791829102996</v>
+        <v>0.21623355088902652</v>
       </c>
       <c r="AQ21" t="s">
         <v>46</v>
       </c>
       <c r="AR21" s="5">
         <f>NPV(AR20,AE14:ES14)</f>
-        <v>5320.5072974069917</v>
+        <v>4980.9369443030428</v>
       </c>
     </row>
     <row r="22" spans="2:44" x14ac:dyDescent="0.3">
@@ -4142,7 +4139,7 @@
       </c>
       <c r="T22" s="10">
         <f t="shared" si="72"/>
-        <v>0.23999999999999996</v>
+        <v>0.25506376594148555</v>
       </c>
       <c r="U22" s="10">
         <f t="shared" si="72"/>
@@ -4182,7 +4179,7 @@
       </c>
       <c r="AE22" s="10">
         <f t="shared" si="74"/>
-        <v>0.229181383438501</v>
+        <v>0.23304890568424552</v>
       </c>
       <c r="AF22" s="10">
         <f t="shared" si="74"/>
@@ -4229,7 +4226,7 @@
       </c>
       <c r="AR22" s="5">
         <f>Main!D8</f>
-        <v>298.2999999999999</v>
+        <v>208.50000000000006</v>
       </c>
     </row>
     <row r="23" spans="2:44" x14ac:dyDescent="0.3">
@@ -4306,7 +4303,7 @@
       </c>
       <c r="T23" s="10">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>-1.5003750937734445E-3</v>
       </c>
       <c r="U23" s="10">
         <f t="shared" si="80"/>
@@ -4346,7 +4343,7 @@
       </c>
       <c r="AE23" s="10">
         <f t="shared" si="82"/>
-        <v>-7.908345439692141E-4</v>
+        <v>-1.2040001701653584E-3</v>
       </c>
       <c r="AF23" s="10">
         <f t="shared" si="82"/>
@@ -4393,7 +4390,7 @@
       </c>
       <c r="AR23" s="5">
         <f>AR21+AR22</f>
-        <v>5618.8072974069919</v>
+        <v>5189.4369443030428</v>
       </c>
     </row>
     <row r="24" spans="2:44" x14ac:dyDescent="0.3">
@@ -4470,7 +4467,7 @@
       </c>
       <c r="T24" s="10">
         <f t="shared" si="85"/>
-        <v>0.16980088888888889</v>
+        <v>0.15761127831458879</v>
       </c>
       <c r="U24" s="10">
         <f t="shared" si="85"/>
@@ -4510,54 +4507,54 @@
       </c>
       <c r="AE24" s="10">
         <f t="shared" si="86"/>
-        <v>0.15387601634190259</v>
+        <v>0.15085166546999873</v>
       </c>
       <c r="AF24" s="10">
         <f t="shared" si="86"/>
-        <v>0.15971571203938772</v>
+        <v>0.15688807093044171</v>
       </c>
       <c r="AG24" s="10">
         <f t="shared" si="86"/>
-        <v>0.16270095523294276</v>
+        <v>0.15981259578186591</v>
       </c>
       <c r="AH24" s="10">
         <f t="shared" si="86"/>
-        <v>0.16427752893668801</v>
+        <v>0.16130072917182395</v>
       </c>
       <c r="AI24" s="10">
         <f t="shared" si="86"/>
-        <v>0.16584057908749519</v>
+        <v>0.16277506138875061</v>
       </c>
       <c r="AJ24" s="10">
         <f t="shared" si="86"/>
-        <v>0.16739025722070691</v>
+        <v>0.1642357354673816</v>
       </c>
       <c r="AK24" s="10">
         <f t="shared" si="86"/>
-        <v>0.16892671357182396</v>
+        <v>0.16431935740420345</v>
       </c>
       <c r="AL24" s="10">
         <f t="shared" si="86"/>
-        <v>0.17045009709107065</v>
+        <v>0.16440463522096233</v>
       </c>
       <c r="AM24" s="10">
         <f t="shared" si="86"/>
-        <v>0.1719605554578349</v>
+        <v>0.16449160170735994</v>
       </c>
       <c r="AN24" s="10">
         <f t="shared" si="86"/>
-        <v>0.17345823509498456</v>
+        <v>0.16458029030239912</v>
       </c>
       <c r="AO24" s="10">
         <f t="shared" ref="AO24" si="87">AO14/AO3</f>
-        <v>0.1749432811830626</v>
+        <v>0.16467073510724115</v>
       </c>
       <c r="AQ24" t="s">
         <v>49</v>
       </c>
       <c r="AR24" s="4">
         <f>AR23/AN15</f>
-        <v>129.46560593103669</v>
+        <v>119.57227982265076</v>
       </c>
     </row>
     <row r="25" spans="2:44" x14ac:dyDescent="0.3">
@@ -4566,7 +4563,7 @@
       </c>
       <c r="AR25" s="4">
         <f>Main!D3</f>
-        <v>70.83</v>
+        <v>81.36</v>
       </c>
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.3">
@@ -4575,7 +4572,7 @@
       </c>
       <c r="AR26" s="12">
         <f>AR24/AR25-1</f>
-        <v>0.82783574659094583</v>
+        <v>0.46966912269728067</v>
       </c>
     </row>
     <row r="27" spans="2:44" x14ac:dyDescent="0.3">
